--- a/SuppXLS/Scen_SYS_CarbonBudget-CAP24_CB1_2.xlsx
+++ b/SuppXLS/Scen_SYS_CarbonBudget-CAP24_CB1_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\TIM 2100\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2558C4DC-E6FC-48EB-AE5B-487179A4CE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03084657-1F66-408C-A90B-2B0CE61A924E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="10690" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
@@ -501,9 +501,6 @@
     <t>\I:</t>
   </si>
   <si>
-    <t>TOTCO2</t>
-  </si>
-  <si>
     <t>AllRegions</t>
   </si>
   <si>
@@ -529,6 +526,9 @@
   </si>
   <si>
     <t>Carbon budget 2</t>
+  </si>
+  <si>
+    <t>TOTCO2INT</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1348,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1793">
+  <cellStyleXfs count="2267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -3212,6 +3212,480 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3306,7 +3780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1793">
+  <cellStyles count="2267">
     <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{EC20F1A7-EAB6-4AF7-B12F-C83CB66D1C43}"/>
     <cellStyle name="20% - Accent1 2 10" xfId="5" xr:uid="{0AA1C8F4-B181-4D14-A44A-1CB316CECB47}"/>
     <cellStyle name="20% - Accent1 2 11" xfId="6" xr:uid="{5C40E15E-BF88-416E-A267-11D1EE226B4C}"/>
@@ -3728,143 +4202,419 @@
     <cellStyle name="Check Cell 2 9" xfId="422" xr:uid="{1E5B0F9E-33A8-4B9D-BCC6-2B636012D487}"/>
     <cellStyle name="Check Cell 3" xfId="423" xr:uid="{E2D18BA2-CB38-4EFD-915A-F314BE325D12}"/>
     <cellStyle name="Comma [0] 2 10" xfId="424" xr:uid="{13EB380C-8B67-47D0-ABB3-848F7E7F6A06}"/>
+    <cellStyle name="Comma [0] 2 10 2" xfId="2030" xr:uid="{81D3BD0B-C198-4190-9AC7-80EEE43860CF}"/>
+    <cellStyle name="Comma [0] 2 10 3" xfId="1793" xr:uid="{B2E604E3-B373-46FB-B787-6B344E4C733D}"/>
     <cellStyle name="Comma [0] 2 2" xfId="425" xr:uid="{9B41DB7B-9578-41A0-9464-BAB21CF784D3}"/>
+    <cellStyle name="Comma [0] 2 2 2" xfId="2031" xr:uid="{A60FCF14-EDA3-4593-8AAA-344FC20C94A5}"/>
+    <cellStyle name="Comma [0] 2 2 3" xfId="1794" xr:uid="{A8240B3A-D6C7-433F-9A12-8C6D78C864F7}"/>
     <cellStyle name="Comma [0] 2 3" xfId="426" xr:uid="{B20579F4-A28E-4668-8D3E-E350234A29E3}"/>
+    <cellStyle name="Comma [0] 2 3 2" xfId="2032" xr:uid="{5E227A8F-20F8-4587-A352-30A39A2B08FB}"/>
+    <cellStyle name="Comma [0] 2 3 3" xfId="1795" xr:uid="{A05E4F80-3DF6-42D4-BF86-D24953D423A9}"/>
     <cellStyle name="Comma [0] 2 4" xfId="427" xr:uid="{F99DB291-37CF-4D96-A1E4-A2937042304D}"/>
+    <cellStyle name="Comma [0] 2 4 2" xfId="2033" xr:uid="{B9BB925D-3FC0-4038-92BC-8C2A40DF4635}"/>
+    <cellStyle name="Comma [0] 2 4 3" xfId="1796" xr:uid="{36CD9AE5-FA09-4C9B-922C-0A3D6559AA95}"/>
     <cellStyle name="Comma [0] 2 5" xfId="428" xr:uid="{09062CA3-FF34-4758-A21B-FA43D38FACC0}"/>
+    <cellStyle name="Comma [0] 2 5 2" xfId="2034" xr:uid="{C0E7894D-3675-41B9-ACFE-C3D6A3F4F769}"/>
+    <cellStyle name="Comma [0] 2 5 3" xfId="1797" xr:uid="{9191A64C-A6E2-44F9-9A31-3114482996CE}"/>
     <cellStyle name="Comma [0] 2 6" xfId="429" xr:uid="{420C9EE9-9BD4-4453-A67D-4D7798AE5CE8}"/>
+    <cellStyle name="Comma [0] 2 6 2" xfId="2035" xr:uid="{4A7C2D51-B95E-49C3-ABB5-9959ED0E3011}"/>
+    <cellStyle name="Comma [0] 2 6 3" xfId="1798" xr:uid="{A8A7B701-7DFF-4042-8982-8BD1BF900037}"/>
     <cellStyle name="Comma [0] 2 7" xfId="430" xr:uid="{86A3E8B6-3870-482B-BBD8-5DB3CE4A19EC}"/>
+    <cellStyle name="Comma [0] 2 7 2" xfId="2036" xr:uid="{A65B4DA0-3649-474E-B769-667CE5A0EF61}"/>
+    <cellStyle name="Comma [0] 2 7 3" xfId="1799" xr:uid="{CF232F9F-319F-4FFA-AA2F-6AFB752479A3}"/>
     <cellStyle name="Comma [0] 2 8" xfId="431" xr:uid="{F416ED8D-0A85-4108-B21A-7D67F7C7D9ED}"/>
+    <cellStyle name="Comma [0] 2 8 2" xfId="2037" xr:uid="{A0FB1074-E3E6-4F71-B2C6-30097BFD5B4A}"/>
+    <cellStyle name="Comma [0] 2 8 3" xfId="1800" xr:uid="{16A91DB0-DF28-4ADA-8FAE-275693B5A9AF}"/>
     <cellStyle name="Comma [0] 2 9" xfId="432" xr:uid="{71F496F2-3D6D-461A-A605-5FA1BE81E5E7}"/>
+    <cellStyle name="Comma [0] 2 9 2" xfId="2038" xr:uid="{9C18AE1A-34D7-473D-8BB8-8612A59DCA6F}"/>
+    <cellStyle name="Comma [0] 2 9 3" xfId="1801" xr:uid="{E6A3585D-9F9C-4C67-9E9A-366FADC8BD86}"/>
     <cellStyle name="Comma 10" xfId="433" xr:uid="{FACB7CC2-FAD8-49C5-A7FB-FD0A0225EC1E}"/>
+    <cellStyle name="Comma 10 10" xfId="1802" xr:uid="{FE1DF2A8-E799-4D7D-A32F-231DDE471373}"/>
     <cellStyle name="Comma 10 2" xfId="434" xr:uid="{2263C691-F6B5-4A7B-9B0E-20A5CA8A80B7}"/>
     <cellStyle name="Comma 10 2 10" xfId="435" xr:uid="{1FE590A1-2E5B-43E8-877A-20DC04F8C509}"/>
+    <cellStyle name="Comma 10 2 10 2" xfId="2041" xr:uid="{6427D0A9-0265-477C-928F-32457C995FAE}"/>
+    <cellStyle name="Comma 10 2 10 3" xfId="1804" xr:uid="{24362591-05E3-4E43-B4E9-83A33774BA62}"/>
     <cellStyle name="Comma 10 2 11" xfId="436" xr:uid="{6B881517-B3BB-4899-AC8C-11E211BF2C81}"/>
+    <cellStyle name="Comma 10 2 11 2" xfId="2042" xr:uid="{C76C16C1-33C6-4408-9584-AA91B61D24E7}"/>
+    <cellStyle name="Comma 10 2 11 3" xfId="1805" xr:uid="{5B5A19DF-5179-4061-A055-1111490BA6E9}"/>
     <cellStyle name="Comma 10 2 12" xfId="437" xr:uid="{BD628869-ED55-4B53-B15A-5F8BA25EC1D8}"/>
+    <cellStyle name="Comma 10 2 12 2" xfId="2043" xr:uid="{BB332FC5-8FF3-4286-BD41-81CBB388777A}"/>
+    <cellStyle name="Comma 10 2 12 3" xfId="1806" xr:uid="{42B52600-6CB4-4001-B26D-AD80BA99072E}"/>
     <cellStyle name="Comma 10 2 13" xfId="438" xr:uid="{30B28322-7CF6-4AEA-89BF-076A5C5CBEEF}"/>
+    <cellStyle name="Comma 10 2 13 2" xfId="2044" xr:uid="{0233660E-96ED-49B0-B3D4-4ED972030FFD}"/>
+    <cellStyle name="Comma 10 2 13 3" xfId="1807" xr:uid="{D3A4A5BE-F9BB-4998-BDE7-9FA7F10ACA9F}"/>
     <cellStyle name="Comma 10 2 14" xfId="439" xr:uid="{C8A83EAC-16E4-4D63-B4A3-184913C2CC38}"/>
+    <cellStyle name="Comma 10 2 14 2" xfId="2045" xr:uid="{9125174F-42A0-48CB-9355-26CA37FB63BF}"/>
+    <cellStyle name="Comma 10 2 14 3" xfId="1808" xr:uid="{BAC0629E-89EF-474D-9338-0CBFFE2D5287}"/>
     <cellStyle name="Comma 10 2 15" xfId="440" xr:uid="{A0D7E326-564C-4316-90D4-98F5E1B5460D}"/>
+    <cellStyle name="Comma 10 2 15 2" xfId="2046" xr:uid="{26FAC52F-E7C8-4E80-842B-E33B9BC47E59}"/>
+    <cellStyle name="Comma 10 2 15 3" xfId="1809" xr:uid="{EF78D597-6F71-4F3A-B7BC-0D1618CF5159}"/>
     <cellStyle name="Comma 10 2 16" xfId="441" xr:uid="{97CA26C2-8674-4AF5-82AB-56AFD0E680F8}"/>
+    <cellStyle name="Comma 10 2 16 2" xfId="2047" xr:uid="{00C5A4A4-4F1C-4B4E-9D09-3D3F77650C32}"/>
+    <cellStyle name="Comma 10 2 16 3" xfId="1810" xr:uid="{641F1125-4603-4BAD-8C55-229E9C06B7C6}"/>
     <cellStyle name="Comma 10 2 17" xfId="442" xr:uid="{C85ACC1E-FED0-4A2E-90C2-5B3458095745}"/>
+    <cellStyle name="Comma 10 2 17 2" xfId="2048" xr:uid="{9DDF2AF1-09CA-46B1-958A-CCB66EFAF6D9}"/>
+    <cellStyle name="Comma 10 2 17 3" xfId="1811" xr:uid="{3B8A6C1D-FE20-4365-B978-FB05EAF1377C}"/>
+    <cellStyle name="Comma 10 2 18" xfId="2040" xr:uid="{0C727DF1-34E4-4960-8671-3A966249B39D}"/>
+    <cellStyle name="Comma 10 2 19" xfId="1803" xr:uid="{3B0E5BBD-81BE-4165-A2EA-7BA820094C27}"/>
     <cellStyle name="Comma 10 2 2" xfId="443" xr:uid="{C1925102-8075-4238-A456-3C73DA5A7BA0}"/>
+    <cellStyle name="Comma 10 2 2 2" xfId="2049" xr:uid="{97A257ED-93C7-4A91-ABEB-75446A316D5F}"/>
+    <cellStyle name="Comma 10 2 2 3" xfId="1812" xr:uid="{318DD32A-EEA3-4A47-BA18-9E9B59159591}"/>
     <cellStyle name="Comma 10 2 3" xfId="444" xr:uid="{FD3F267A-69BE-4C3F-B406-26C0BD166197}"/>
+    <cellStyle name="Comma 10 2 3 2" xfId="2050" xr:uid="{AD189E75-05D2-46DC-8B1D-C9473645121B}"/>
+    <cellStyle name="Comma 10 2 3 3" xfId="1813" xr:uid="{0436E96E-0B7E-4BD1-A3EF-9B34FEB44C20}"/>
     <cellStyle name="Comma 10 2 4" xfId="445" xr:uid="{24028179-7BBB-4941-ADBA-5FF9E670A5EA}"/>
+    <cellStyle name="Comma 10 2 4 2" xfId="2051" xr:uid="{8986DFFF-8BC8-4006-A5A5-EE528DE58448}"/>
+    <cellStyle name="Comma 10 2 4 3" xfId="1814" xr:uid="{924CF2E1-45AC-4065-B5C6-BB73290E2053}"/>
     <cellStyle name="Comma 10 2 5" xfId="446" xr:uid="{96EF4079-2C09-4445-920C-1B210E2186E8}"/>
+    <cellStyle name="Comma 10 2 5 2" xfId="2052" xr:uid="{30F78FD1-11F5-4DAA-98B5-B078EB4AAFCE}"/>
+    <cellStyle name="Comma 10 2 5 3" xfId="1815" xr:uid="{4D856331-18D9-49A4-84C3-F41366974183}"/>
     <cellStyle name="Comma 10 2 6" xfId="447" xr:uid="{384F9C5F-979E-4446-B6E1-B27E928070CB}"/>
+    <cellStyle name="Comma 10 2 6 2" xfId="2053" xr:uid="{68F7F548-FFD5-4FBF-B7EA-806896C6140B}"/>
+    <cellStyle name="Comma 10 2 6 3" xfId="1816" xr:uid="{ACF36B2B-F688-4884-B794-721F59D37841}"/>
     <cellStyle name="Comma 10 2 7" xfId="448" xr:uid="{5667CD28-63D0-4438-AA32-096D0993FF97}"/>
+    <cellStyle name="Comma 10 2 7 2" xfId="2054" xr:uid="{8048AD19-09B0-4C3A-91CA-15F0EB85C1BD}"/>
+    <cellStyle name="Comma 10 2 7 3" xfId="1817" xr:uid="{F9F89B03-3D63-4C5C-A563-76DC3AEACAA7}"/>
     <cellStyle name="Comma 10 2 8" xfId="449" xr:uid="{F8127A2E-74D8-4263-A49B-960FB64EA53D}"/>
+    <cellStyle name="Comma 10 2 8 2" xfId="2055" xr:uid="{9719B6A5-E809-4395-80B5-8BF3351F6555}"/>
+    <cellStyle name="Comma 10 2 8 3" xfId="1818" xr:uid="{EB0798F9-6E68-42AB-A2BD-D50E61363646}"/>
     <cellStyle name="Comma 10 2 9" xfId="450" xr:uid="{667D6EB3-3197-493E-A960-C99F69E6403A}"/>
+    <cellStyle name="Comma 10 2 9 2" xfId="2056" xr:uid="{A03D1638-57B9-49E4-B052-5CB2ACA1DD84}"/>
+    <cellStyle name="Comma 10 2 9 3" xfId="1819" xr:uid="{4CA501E4-9391-40C4-962D-6826CC36B048}"/>
     <cellStyle name="Comma 10 3" xfId="451" xr:uid="{2381A7A8-2023-4F4E-AB35-452793AEC217}"/>
     <cellStyle name="Comma 10 3 10" xfId="452" xr:uid="{09B9AFB5-D928-4B56-9EAE-370E0B1682E2}"/>
+    <cellStyle name="Comma 10 3 10 2" xfId="2058" xr:uid="{CF1DBB84-1C3A-45D2-992C-535BC38D3A42}"/>
+    <cellStyle name="Comma 10 3 10 3" xfId="1821" xr:uid="{B941BBC8-5A2B-4D1D-B8BF-13DB3BB93A51}"/>
     <cellStyle name="Comma 10 3 11" xfId="453" xr:uid="{39C178CB-E75C-47C7-AD57-E00DD6D7D487}"/>
+    <cellStyle name="Comma 10 3 11 2" xfId="2059" xr:uid="{4A638B86-CF80-4B9A-B381-BDCFDC300835}"/>
+    <cellStyle name="Comma 10 3 11 3" xfId="1822" xr:uid="{4F92AF3C-FD88-4D0F-9D48-02B97983A711}"/>
     <cellStyle name="Comma 10 3 12" xfId="454" xr:uid="{91281440-DF20-4066-A3BE-72878614B717}"/>
+    <cellStyle name="Comma 10 3 12 2" xfId="2060" xr:uid="{D9A7F1FF-F604-4352-B541-C4777BC184F2}"/>
+    <cellStyle name="Comma 10 3 12 3" xfId="1823" xr:uid="{FB3A73CB-854A-4B8A-B9AC-CF0FA18701EA}"/>
     <cellStyle name="Comma 10 3 13" xfId="455" xr:uid="{6DCDE1A2-0500-42BD-8681-C32C54574268}"/>
+    <cellStyle name="Comma 10 3 13 2" xfId="2061" xr:uid="{068F2D9F-7ADF-498B-AE46-62E7806CFBD0}"/>
+    <cellStyle name="Comma 10 3 13 3" xfId="1824" xr:uid="{5CD9F9B2-AD77-4123-98E5-E968A298C091}"/>
     <cellStyle name="Comma 10 3 14" xfId="456" xr:uid="{D1FC7552-9B5B-4176-A68E-1707BD3FE8FD}"/>
+    <cellStyle name="Comma 10 3 14 2" xfId="2062" xr:uid="{4007BEED-105F-4902-A81D-14106D46627B}"/>
+    <cellStyle name="Comma 10 3 14 3" xfId="1825" xr:uid="{858C2BAB-55BA-40EF-85B9-E58CD67F12AA}"/>
     <cellStyle name="Comma 10 3 15" xfId="457" xr:uid="{262256C6-7761-4BA3-B36C-7BDF70310827}"/>
+    <cellStyle name="Comma 10 3 15 2" xfId="2063" xr:uid="{96318412-AD56-4ACB-AA81-E1C593B6C944}"/>
+    <cellStyle name="Comma 10 3 15 3" xfId="1826" xr:uid="{30FA8A9F-7411-428F-A6D0-42F7F06A6E1D}"/>
     <cellStyle name="Comma 10 3 16" xfId="458" xr:uid="{2E87924F-A98C-486B-B33D-6DD404E94618}"/>
+    <cellStyle name="Comma 10 3 16 2" xfId="2064" xr:uid="{6D56CA10-7B5C-47FC-ACE6-9C769FFF5CD8}"/>
+    <cellStyle name="Comma 10 3 16 3" xfId="1827" xr:uid="{3CDDCD4B-9A9E-4E83-9C1A-2BC24959CA28}"/>
     <cellStyle name="Comma 10 3 17" xfId="459" xr:uid="{AE3306BD-7812-4A2B-B632-F0DE75835457}"/>
+    <cellStyle name="Comma 10 3 17 2" xfId="2065" xr:uid="{9CCE9400-B527-4BF5-A55E-1BA88D39EEFB}"/>
+    <cellStyle name="Comma 10 3 17 3" xfId="1828" xr:uid="{F3BC8DCC-518B-4FD8-BCF3-FB39471CD2A5}"/>
+    <cellStyle name="Comma 10 3 18" xfId="2057" xr:uid="{4BF278D4-6E1A-4491-879C-004B8AE2FD73}"/>
+    <cellStyle name="Comma 10 3 19" xfId="1820" xr:uid="{0104D69E-03D4-4363-A5DF-2553FC5A1C62}"/>
     <cellStyle name="Comma 10 3 2" xfId="460" xr:uid="{EF248761-FC48-42E2-88D1-F6B0D82541C0}"/>
+    <cellStyle name="Comma 10 3 2 2" xfId="2066" xr:uid="{5E5A1CC5-F059-4FBA-9963-8546EDCC2D09}"/>
+    <cellStyle name="Comma 10 3 2 3" xfId="1829" xr:uid="{FBF4AF6E-BC37-4CCC-B16B-A3BF2BD34D63}"/>
     <cellStyle name="Comma 10 3 3" xfId="461" xr:uid="{9E703699-1895-4028-B214-75B2CF8DD812}"/>
+    <cellStyle name="Comma 10 3 3 2" xfId="2067" xr:uid="{99760FF1-E3F5-4DB0-AC91-BB50F329C3A6}"/>
+    <cellStyle name="Comma 10 3 3 3" xfId="1830" xr:uid="{6CF65946-5581-4C6E-A1F4-880E200E73C5}"/>
     <cellStyle name="Comma 10 3 4" xfId="462" xr:uid="{D79785E9-6B06-4CE6-9069-1695AC4CCF66}"/>
+    <cellStyle name="Comma 10 3 4 2" xfId="2068" xr:uid="{B562163E-EB6B-4726-8A1E-49BD036C9D13}"/>
+    <cellStyle name="Comma 10 3 4 3" xfId="1831" xr:uid="{277E718C-3FA8-4209-8AFA-7C92A40CD3DE}"/>
     <cellStyle name="Comma 10 3 5" xfId="463" xr:uid="{85119826-DC66-4F53-8B60-D1D61F5A6BB4}"/>
+    <cellStyle name="Comma 10 3 5 2" xfId="2069" xr:uid="{9BCFFAE8-6AFF-42FF-BEE9-93E4FC11364A}"/>
+    <cellStyle name="Comma 10 3 5 3" xfId="1832" xr:uid="{970052D2-7542-40DC-9A2F-7061F5804FAA}"/>
     <cellStyle name="Comma 10 3 6" xfId="464" xr:uid="{0AF73299-6D7D-4CD4-A022-AE8EBD765AB6}"/>
+    <cellStyle name="Comma 10 3 6 2" xfId="2070" xr:uid="{632F4101-8948-419C-871E-26F49B9AA448}"/>
+    <cellStyle name="Comma 10 3 6 3" xfId="1833" xr:uid="{DC839422-D3AE-4FDF-BE2C-AD8D591883BD}"/>
     <cellStyle name="Comma 10 3 7" xfId="465" xr:uid="{4F7ED5E2-D659-4222-A3F3-5273695C83A7}"/>
+    <cellStyle name="Comma 10 3 7 2" xfId="2071" xr:uid="{359CB476-BC69-47F9-98E6-84654D4D206F}"/>
+    <cellStyle name="Comma 10 3 7 3" xfId="1834" xr:uid="{1F9335B2-AA12-4B46-BDBE-09F9701AE2C0}"/>
     <cellStyle name="Comma 10 3 8" xfId="466" xr:uid="{075BA881-751A-46B2-861D-CD260E702453}"/>
+    <cellStyle name="Comma 10 3 8 2" xfId="2072" xr:uid="{EF256540-B3B8-4906-BD77-B05F07882060}"/>
+    <cellStyle name="Comma 10 3 8 3" xfId="1835" xr:uid="{B4066CB5-6370-4485-B437-F3A13AE06C01}"/>
     <cellStyle name="Comma 10 3 9" xfId="467" xr:uid="{1372429F-5912-4505-8DC9-F68CF550475B}"/>
+    <cellStyle name="Comma 10 3 9 2" xfId="2073" xr:uid="{324048E2-B5CD-4E6C-BD59-8DF834ECDACF}"/>
+    <cellStyle name="Comma 10 3 9 3" xfId="1836" xr:uid="{0352ECC8-823E-4C26-94DB-D2D2C350B2C2}"/>
     <cellStyle name="Comma 10 4" xfId="468" xr:uid="{892B04F6-1C8D-4200-B6CB-B0148ABBC55A}"/>
     <cellStyle name="Comma 10 4 10" xfId="469" xr:uid="{D51D1FD0-3934-47D0-81E8-F9EC6EAEAF50}"/>
+    <cellStyle name="Comma 10 4 10 2" xfId="2075" xr:uid="{20AB36C8-ECAD-4690-8579-E2D97A1A46DC}"/>
+    <cellStyle name="Comma 10 4 10 3" xfId="1838" xr:uid="{C208411B-21D8-4E39-B29C-220C26747336}"/>
     <cellStyle name="Comma 10 4 11" xfId="470" xr:uid="{B4BB2DBA-B643-4826-8260-58251C0AA8A2}"/>
+    <cellStyle name="Comma 10 4 11 2" xfId="2076" xr:uid="{1EF53F2B-139E-48D2-A04E-A2491C9123D7}"/>
+    <cellStyle name="Comma 10 4 11 3" xfId="1839" xr:uid="{A17D3E79-D53E-4705-8373-D836022A9AF2}"/>
     <cellStyle name="Comma 10 4 12" xfId="471" xr:uid="{1DE4F001-9A27-41E7-AF74-FEC4BAB181D0}"/>
+    <cellStyle name="Comma 10 4 12 2" xfId="2077" xr:uid="{4152A536-4E25-4978-8FDA-6FAA381F5AD9}"/>
+    <cellStyle name="Comma 10 4 12 3" xfId="1840" xr:uid="{C85F3D19-2B68-4D95-86E9-E324D2E8D3F2}"/>
     <cellStyle name="Comma 10 4 13" xfId="472" xr:uid="{56A5CC37-5114-42AD-84D7-741989675CE0}"/>
+    <cellStyle name="Comma 10 4 13 2" xfId="2078" xr:uid="{7A3E0762-E817-4859-902F-89A279397671}"/>
+    <cellStyle name="Comma 10 4 13 3" xfId="1841" xr:uid="{D08BA79B-1639-4CF2-AB07-427A582DE80A}"/>
     <cellStyle name="Comma 10 4 14" xfId="473" xr:uid="{86DE866D-0C30-4A2B-89EF-4FAE0F4BA18A}"/>
+    <cellStyle name="Comma 10 4 14 2" xfId="2079" xr:uid="{C3F9E542-3D4F-4D72-AD7C-4AB887DBBFCD}"/>
+    <cellStyle name="Comma 10 4 14 3" xfId="1842" xr:uid="{3DF96EB0-B932-4EDE-9AA6-0A5A1F102416}"/>
     <cellStyle name="Comma 10 4 15" xfId="474" xr:uid="{587C1285-C282-42FC-8727-669515C5C4E1}"/>
+    <cellStyle name="Comma 10 4 15 2" xfId="2080" xr:uid="{29AB803D-5C1F-45C0-B5FB-05A0BBA3531B}"/>
+    <cellStyle name="Comma 10 4 15 3" xfId="1843" xr:uid="{AB50EEC3-DBFE-4E8E-A246-0417FAFBB84C}"/>
     <cellStyle name="Comma 10 4 16" xfId="475" xr:uid="{C9DB269C-B52F-4310-9FE0-E49C69A3DD92}"/>
+    <cellStyle name="Comma 10 4 16 2" xfId="2081" xr:uid="{CD8D78A6-23AA-4B50-BDEB-F3AD20D7D930}"/>
+    <cellStyle name="Comma 10 4 16 3" xfId="1844" xr:uid="{5E2B8D75-2113-4A1B-BF01-146DEC303CA2}"/>
     <cellStyle name="Comma 10 4 17" xfId="476" xr:uid="{5B0B247E-2D09-4373-9997-987D8E01404A}"/>
+    <cellStyle name="Comma 10 4 17 2" xfId="2082" xr:uid="{8695CFC4-C188-48EB-95B2-7C7FC8B85333}"/>
+    <cellStyle name="Comma 10 4 17 3" xfId="1845" xr:uid="{A3115DC5-363E-4ABA-A852-56666BDAAFB6}"/>
+    <cellStyle name="Comma 10 4 18" xfId="2074" xr:uid="{1DB862C6-2112-4A7F-918C-6DB5AE9CDFE8}"/>
+    <cellStyle name="Comma 10 4 19" xfId="1837" xr:uid="{60F30AAD-9C41-4AA5-AC82-8D0BF89ED6A5}"/>
     <cellStyle name="Comma 10 4 2" xfId="477" xr:uid="{34BC0AC7-6F9F-4E67-864D-6997555F00F4}"/>
+    <cellStyle name="Comma 10 4 2 2" xfId="2083" xr:uid="{F351AF0A-BCD8-4087-8BF5-D46CF9700713}"/>
+    <cellStyle name="Comma 10 4 2 3" xfId="1846" xr:uid="{591045CE-A58B-4B0B-95E2-28EFF8D78023}"/>
     <cellStyle name="Comma 10 4 3" xfId="478" xr:uid="{125FA83B-21DB-49F6-949E-F150DF911BF4}"/>
+    <cellStyle name="Comma 10 4 3 2" xfId="2084" xr:uid="{0E660D73-6C66-422D-99DE-2F45C5E5E359}"/>
+    <cellStyle name="Comma 10 4 3 3" xfId="1847" xr:uid="{1A91EA31-5A81-4C78-A6DA-46A15A1064E7}"/>
     <cellStyle name="Comma 10 4 4" xfId="479" xr:uid="{944395A3-365A-4752-9911-008A867FB71B}"/>
+    <cellStyle name="Comma 10 4 4 2" xfId="2085" xr:uid="{2991FB5E-85EB-4A90-94FA-321377A4B7AB}"/>
+    <cellStyle name="Comma 10 4 4 3" xfId="1848" xr:uid="{DC43ADD0-77FB-4DE8-802F-96A57C80F631}"/>
     <cellStyle name="Comma 10 4 5" xfId="480" xr:uid="{4770F347-07A0-4D01-975C-486B70040E6F}"/>
+    <cellStyle name="Comma 10 4 5 2" xfId="2086" xr:uid="{2835D132-C7E6-4F8A-BAF5-B4DDBF29AE93}"/>
+    <cellStyle name="Comma 10 4 5 3" xfId="1849" xr:uid="{5FE8CC64-3E82-431B-B5D6-C880A6861B89}"/>
     <cellStyle name="Comma 10 4 6" xfId="481" xr:uid="{CF87A2E2-A29A-4783-8F42-67DF147BA5B5}"/>
+    <cellStyle name="Comma 10 4 6 2" xfId="2087" xr:uid="{4F122CCD-434C-47CB-8981-0B042579CA80}"/>
+    <cellStyle name="Comma 10 4 6 3" xfId="1850" xr:uid="{35BF8042-E368-4B2B-A989-F3634F1F2843}"/>
     <cellStyle name="Comma 10 4 7" xfId="482" xr:uid="{7BD8EC99-E45C-4F55-9C08-FCB6F7452BBE}"/>
+    <cellStyle name="Comma 10 4 7 2" xfId="2088" xr:uid="{55D77E27-C143-42E2-A5D3-45AEFB6FB832}"/>
+    <cellStyle name="Comma 10 4 7 3" xfId="1851" xr:uid="{414AF4BA-440F-4E8F-BC98-78F260FB9B57}"/>
     <cellStyle name="Comma 10 4 8" xfId="483" xr:uid="{E33ADC4E-0865-4F3D-9869-267A3CB3CE2D}"/>
+    <cellStyle name="Comma 10 4 8 2" xfId="2089" xr:uid="{5D27074B-F9C0-4097-8B25-7826F190DEEE}"/>
+    <cellStyle name="Comma 10 4 8 3" xfId="1852" xr:uid="{799391F8-75C4-42C4-ABA3-CDE4FA984D42}"/>
     <cellStyle name="Comma 10 4 9" xfId="484" xr:uid="{E77DD074-7DF6-44F2-8A20-96A039773276}"/>
+    <cellStyle name="Comma 10 4 9 2" xfId="2090" xr:uid="{E8A49298-5D70-4DF3-8C5D-CDA4C7CE20D3}"/>
+    <cellStyle name="Comma 10 4 9 3" xfId="1853" xr:uid="{FBFD8313-8ECB-4EF7-A6F2-D6A6D284EE7B}"/>
     <cellStyle name="Comma 10 5" xfId="485" xr:uid="{EC48B89A-380D-4016-93DF-FACF735A6EEE}"/>
     <cellStyle name="Comma 10 5 10" xfId="486" xr:uid="{4619FB2C-D1A8-4ABC-B11D-24AEC8C3C9B2}"/>
+    <cellStyle name="Comma 10 5 10 2" xfId="2092" xr:uid="{C795A902-927E-43F3-BB26-852BE4E36E69}"/>
+    <cellStyle name="Comma 10 5 10 3" xfId="1855" xr:uid="{D3F6431A-5523-4F2F-AF0F-2B05BD05BE4F}"/>
     <cellStyle name="Comma 10 5 11" xfId="487" xr:uid="{F91B25A1-62EE-4434-AFDE-F23A51E98AB5}"/>
+    <cellStyle name="Comma 10 5 11 2" xfId="2093" xr:uid="{E9AF5C16-DA18-437F-8946-CB17980A4D66}"/>
+    <cellStyle name="Comma 10 5 11 3" xfId="1856" xr:uid="{BE48776F-6D88-4669-95AE-D594E646D4C9}"/>
     <cellStyle name="Comma 10 5 12" xfId="488" xr:uid="{F76C0732-DBA2-4189-928C-11DCA3256D02}"/>
+    <cellStyle name="Comma 10 5 12 2" xfId="2094" xr:uid="{4E2F4DF1-2407-43AC-B97B-A55A6EA2EBA7}"/>
+    <cellStyle name="Comma 10 5 12 3" xfId="1857" xr:uid="{7563A70C-BC40-4DAA-A281-92C22A3BAA3E}"/>
     <cellStyle name="Comma 10 5 13" xfId="489" xr:uid="{B6BACA9E-DC74-48BD-95FC-D5E38906BCDE}"/>
+    <cellStyle name="Comma 10 5 13 2" xfId="2095" xr:uid="{566164FF-9430-48A0-A8B0-CD993BF493DE}"/>
+    <cellStyle name="Comma 10 5 13 3" xfId="1858" xr:uid="{0F753610-8A53-454D-ADE6-BB6A0DC673C2}"/>
     <cellStyle name="Comma 10 5 14" xfId="490" xr:uid="{70912F5E-D243-4A25-B244-069C249198E5}"/>
+    <cellStyle name="Comma 10 5 14 2" xfId="2096" xr:uid="{5052548E-5FA2-469C-9A5C-66A492312B6E}"/>
+    <cellStyle name="Comma 10 5 14 3" xfId="1859" xr:uid="{43CB1EB1-80A9-4581-BE36-8051FFBBDA64}"/>
     <cellStyle name="Comma 10 5 15" xfId="491" xr:uid="{7069C481-AF24-4FE7-A871-7EEB2C3EB464}"/>
+    <cellStyle name="Comma 10 5 15 2" xfId="2097" xr:uid="{97D44C58-07EE-420A-9E89-CBF90D5A5204}"/>
+    <cellStyle name="Comma 10 5 15 3" xfId="1860" xr:uid="{E07F55EE-DA99-44A6-BA2C-F28CA7F4068F}"/>
     <cellStyle name="Comma 10 5 16" xfId="492" xr:uid="{91D3B5EC-E818-4D6D-B80A-66FF5509A57D}"/>
+    <cellStyle name="Comma 10 5 16 2" xfId="2098" xr:uid="{68C0FF02-DDF7-44C7-8E6B-97B77F4FB489}"/>
+    <cellStyle name="Comma 10 5 16 3" xfId="1861" xr:uid="{1C400574-34E3-42E5-A819-234D0D8DDDF4}"/>
     <cellStyle name="Comma 10 5 17" xfId="493" xr:uid="{53B70FEB-E00A-4A73-9073-938DA9D8D21C}"/>
+    <cellStyle name="Comma 10 5 17 2" xfId="2099" xr:uid="{27B6A9AF-51C4-40F7-94D0-4513A26EB0F8}"/>
+    <cellStyle name="Comma 10 5 17 3" xfId="1862" xr:uid="{5AA2A641-C17F-44F8-8513-1D5D11AC4B78}"/>
+    <cellStyle name="Comma 10 5 18" xfId="2091" xr:uid="{12B67C11-6C17-4498-B096-0171DB83989F}"/>
+    <cellStyle name="Comma 10 5 19" xfId="1854" xr:uid="{2C4940FA-8383-4400-B8EB-C0E47A9EF79E}"/>
     <cellStyle name="Comma 10 5 2" xfId="494" xr:uid="{C4D056B1-1CC6-4277-821A-9FFDBA5755DE}"/>
+    <cellStyle name="Comma 10 5 2 2" xfId="2100" xr:uid="{8B6C78F7-62B9-44AB-B9D7-8B06B8251E16}"/>
+    <cellStyle name="Comma 10 5 2 3" xfId="1863" xr:uid="{C8208371-87A6-404C-A5B2-AEC1406B53CB}"/>
     <cellStyle name="Comma 10 5 3" xfId="495" xr:uid="{0D48A024-B61B-4D88-9BA4-56C2AD188725}"/>
+    <cellStyle name="Comma 10 5 3 2" xfId="2101" xr:uid="{AD49A683-F35E-41E0-853F-41F0D32D8AF7}"/>
+    <cellStyle name="Comma 10 5 3 3" xfId="1864" xr:uid="{293A0C5B-90B0-4605-A94D-1A21F15E0304}"/>
     <cellStyle name="Comma 10 5 4" xfId="496" xr:uid="{369665A0-C3C5-4253-A704-389C6F23437D}"/>
+    <cellStyle name="Comma 10 5 4 2" xfId="2102" xr:uid="{9A9B0D28-827C-4EC9-9E40-F74BF93517BF}"/>
+    <cellStyle name="Comma 10 5 4 3" xfId="1865" xr:uid="{3F7456EF-2520-4100-A9CD-DD4594FC82D1}"/>
     <cellStyle name="Comma 10 5 5" xfId="497" xr:uid="{18AE6F47-E6F5-480F-BBA9-4C3ABB78EB5A}"/>
+    <cellStyle name="Comma 10 5 5 2" xfId="2103" xr:uid="{9B17DC4D-DD61-4E9E-85D5-DCA24FB25F98}"/>
+    <cellStyle name="Comma 10 5 5 3" xfId="1866" xr:uid="{987F708F-F717-42C2-8F6A-42086C361C28}"/>
     <cellStyle name="Comma 10 5 6" xfId="498" xr:uid="{469C65DB-0103-45B0-9D7E-DC3754CED391}"/>
+    <cellStyle name="Comma 10 5 6 2" xfId="2104" xr:uid="{FC6C03F4-E3BF-462C-8CE9-D45D0704C2B9}"/>
+    <cellStyle name="Comma 10 5 6 3" xfId="1867" xr:uid="{817AAFAA-02F0-4BD8-97F4-48F8EE4CCA94}"/>
     <cellStyle name="Comma 10 5 7" xfId="499" xr:uid="{2E8C6864-4F56-4C44-A1B3-4BA229646584}"/>
+    <cellStyle name="Comma 10 5 7 2" xfId="2105" xr:uid="{71CACB10-2442-44B3-B491-9507C32F8F20}"/>
+    <cellStyle name="Comma 10 5 7 3" xfId="1868" xr:uid="{81B6B980-1E9D-4329-A665-7B7C3F3F584F}"/>
     <cellStyle name="Comma 10 5 8" xfId="500" xr:uid="{BD4A1BC6-78E9-4B4F-8367-7B4DFEA88346}"/>
+    <cellStyle name="Comma 10 5 8 2" xfId="2106" xr:uid="{5207DEF4-0248-4EF1-98B9-76C14340B68B}"/>
+    <cellStyle name="Comma 10 5 8 3" xfId="1869" xr:uid="{82B3AE35-7E63-4AB4-BED5-1682C8D23A0A}"/>
     <cellStyle name="Comma 10 5 9" xfId="501" xr:uid="{5625D8E9-A685-426C-8DDB-5A7F7CC6B2E9}"/>
+    <cellStyle name="Comma 10 5 9 2" xfId="2107" xr:uid="{3F39A2B6-0105-43C4-AE59-AE9476292241}"/>
+    <cellStyle name="Comma 10 5 9 3" xfId="1870" xr:uid="{A999C23A-F566-4D0F-B335-8A297A7E1F9F}"/>
     <cellStyle name="Comma 10 6" xfId="502" xr:uid="{47BC3296-AB68-424D-9B90-35242DF2F3AD}"/>
     <cellStyle name="Comma 10 6 10" xfId="503" xr:uid="{6BDED176-D793-48C2-872C-7E12F90783F0}"/>
+    <cellStyle name="Comma 10 6 10 2" xfId="2109" xr:uid="{B1EF881A-AE1F-4C03-AFD6-9F1BF2BA466A}"/>
+    <cellStyle name="Comma 10 6 10 3" xfId="1872" xr:uid="{E8D64DDF-6557-4451-A869-50425213B58F}"/>
     <cellStyle name="Comma 10 6 11" xfId="504" xr:uid="{1DB0BB9E-5D07-471B-BF33-00612DFB42C2}"/>
+    <cellStyle name="Comma 10 6 11 2" xfId="2110" xr:uid="{BE62202C-D00D-4B79-B407-4D1DFF6F1040}"/>
+    <cellStyle name="Comma 10 6 11 3" xfId="1873" xr:uid="{EDE4B9B8-2457-4456-BD13-B783A0D58C9B}"/>
     <cellStyle name="Comma 10 6 12" xfId="505" xr:uid="{DC954738-CF7E-47CB-908C-FB79353358D4}"/>
+    <cellStyle name="Comma 10 6 12 2" xfId="2111" xr:uid="{FBCF6F3D-089C-491C-A651-5C08B3AAB4C0}"/>
+    <cellStyle name="Comma 10 6 12 3" xfId="1874" xr:uid="{0E4E73DB-D29A-474C-9FBA-54ED07F24980}"/>
     <cellStyle name="Comma 10 6 13" xfId="506" xr:uid="{B7BF1276-AE6A-4CDA-AA6F-75602CDDF224}"/>
+    <cellStyle name="Comma 10 6 13 2" xfId="2112" xr:uid="{C0DE13C6-F00E-402A-AA1C-7FC72CF38F0C}"/>
+    <cellStyle name="Comma 10 6 13 3" xfId="1875" xr:uid="{0A4B852A-AFA1-417B-93F7-1498A51A9774}"/>
     <cellStyle name="Comma 10 6 14" xfId="507" xr:uid="{D381F0BD-AE39-4EFE-B0A4-1ADD3B930716}"/>
+    <cellStyle name="Comma 10 6 14 2" xfId="2113" xr:uid="{30BEF654-CDD7-4255-BB28-B79425F70C24}"/>
+    <cellStyle name="Comma 10 6 14 3" xfId="1876" xr:uid="{E4A050A3-CAB2-45C7-8AD1-5423206CB6C5}"/>
     <cellStyle name="Comma 10 6 15" xfId="508" xr:uid="{867C7129-0FFE-41DC-8776-3AD2B5A68EAE}"/>
+    <cellStyle name="Comma 10 6 15 2" xfId="2114" xr:uid="{E834E373-752C-4ACC-A608-8F58BFDD3125}"/>
+    <cellStyle name="Comma 10 6 15 3" xfId="1877" xr:uid="{D66FA484-5C72-44C1-ADE4-EF5B3D2FBF44}"/>
     <cellStyle name="Comma 10 6 16" xfId="509" xr:uid="{5FA8BCF6-89CF-4FD2-961B-FA9F6A3622F5}"/>
+    <cellStyle name="Comma 10 6 16 2" xfId="2115" xr:uid="{EFB2E4C0-7467-4882-8DBE-1DB1DF3A15CB}"/>
+    <cellStyle name="Comma 10 6 16 3" xfId="1878" xr:uid="{97840258-1582-49B5-9E5C-D1FAD785862B}"/>
     <cellStyle name="Comma 10 6 17" xfId="510" xr:uid="{709DDFD6-62EE-4D77-B413-5752179549C7}"/>
+    <cellStyle name="Comma 10 6 17 2" xfId="2116" xr:uid="{2B6A842A-F3F8-4EF3-9719-4BBA1081CF45}"/>
+    <cellStyle name="Comma 10 6 17 3" xfId="1879" xr:uid="{BD4C63F1-DE95-4014-9CDC-2B95F381A378}"/>
+    <cellStyle name="Comma 10 6 18" xfId="2108" xr:uid="{5D035D63-8008-44A9-B085-72D92BB674CB}"/>
+    <cellStyle name="Comma 10 6 19" xfId="1871" xr:uid="{9A2CEF40-1A9A-4593-81E7-5AA1ACACD241}"/>
     <cellStyle name="Comma 10 6 2" xfId="511" xr:uid="{505EC601-2BC3-44CC-8673-1079F53DF5BB}"/>
+    <cellStyle name="Comma 10 6 2 2" xfId="2117" xr:uid="{6B805EB8-3D39-44F0-9CE6-88D3F34F0EDD}"/>
+    <cellStyle name="Comma 10 6 2 3" xfId="1880" xr:uid="{8D8A132B-FD00-4491-B11F-AF12B1FAD729}"/>
     <cellStyle name="Comma 10 6 3" xfId="512" xr:uid="{4B129687-FE89-455B-BBD0-8601E256F063}"/>
+    <cellStyle name="Comma 10 6 3 2" xfId="2118" xr:uid="{027565FA-FD97-412B-92ED-3C7D2CE59955}"/>
+    <cellStyle name="Comma 10 6 3 3" xfId="1881" xr:uid="{B7DD7190-7518-418B-8BBE-0002EA064551}"/>
     <cellStyle name="Comma 10 6 4" xfId="513" xr:uid="{0019BDC9-A9C5-4070-ABB9-B035E3806585}"/>
+    <cellStyle name="Comma 10 6 4 2" xfId="2119" xr:uid="{189584AC-2857-478E-838F-A0790910232C}"/>
+    <cellStyle name="Comma 10 6 4 3" xfId="1882" xr:uid="{331C2319-1D9A-4474-ADB8-D3CDFA1EB65B}"/>
     <cellStyle name="Comma 10 6 5" xfId="514" xr:uid="{0FA8AB4D-22CC-461C-88E5-A11EFB95F973}"/>
+    <cellStyle name="Comma 10 6 5 2" xfId="2120" xr:uid="{AB2FAC1E-81D2-45B8-B268-203AF9B7BE94}"/>
+    <cellStyle name="Comma 10 6 5 3" xfId="1883" xr:uid="{61EAF353-972E-4803-846B-5BD19723E84E}"/>
     <cellStyle name="Comma 10 6 6" xfId="515" xr:uid="{C0DCF806-D2B7-4235-9F11-5B69C28F3AEA}"/>
+    <cellStyle name="Comma 10 6 6 2" xfId="2121" xr:uid="{1D7D5C2A-09BF-4306-94E0-0A6F75E25BBE}"/>
+    <cellStyle name="Comma 10 6 6 3" xfId="1884" xr:uid="{27136655-4731-4FAD-854A-F0A07179444B}"/>
     <cellStyle name="Comma 10 6 7" xfId="516" xr:uid="{D4E14B77-9A21-498A-B8DD-EF6C85613129}"/>
+    <cellStyle name="Comma 10 6 7 2" xfId="2122" xr:uid="{572320EF-41DB-49D1-AFD8-9A58047FFDA4}"/>
+    <cellStyle name="Comma 10 6 7 3" xfId="1885" xr:uid="{46A72F92-E614-4A8E-A190-6EB5804E2076}"/>
     <cellStyle name="Comma 10 6 8" xfId="517" xr:uid="{E1EF985F-47A2-4327-9D17-ED91A7B4E469}"/>
+    <cellStyle name="Comma 10 6 8 2" xfId="2123" xr:uid="{3C813493-E9AD-4815-B979-5CC1A9F99DE2}"/>
+    <cellStyle name="Comma 10 6 8 3" xfId="1886" xr:uid="{011A1130-06D7-4729-9F86-CB2DC1B64480}"/>
     <cellStyle name="Comma 10 6 9" xfId="518" xr:uid="{B3EB464A-BDB6-4832-A37D-6B49E23D161A}"/>
+    <cellStyle name="Comma 10 6 9 2" xfId="2124" xr:uid="{4A2D1851-04AF-41B1-9DED-729ACA2BF241}"/>
+    <cellStyle name="Comma 10 6 9 3" xfId="1887" xr:uid="{C8F18736-37D6-46A5-BBEA-7505693D0A47}"/>
     <cellStyle name="Comma 10 7" xfId="519" xr:uid="{C84A0D48-D814-4EAA-AEE6-0C9DB1841F52}"/>
     <cellStyle name="Comma 10 7 10" xfId="520" xr:uid="{1B147311-CC56-4301-8D28-8E62EE4270D1}"/>
+    <cellStyle name="Comma 10 7 10 2" xfId="2126" xr:uid="{8FCFFF38-E464-45AB-A4D7-E16D2361FE13}"/>
+    <cellStyle name="Comma 10 7 10 3" xfId="1889" xr:uid="{958F13D7-5048-4526-BBC8-B38F6A4BBC67}"/>
     <cellStyle name="Comma 10 7 11" xfId="521" xr:uid="{0445B5FA-CF84-45C9-812B-0DD40099227E}"/>
+    <cellStyle name="Comma 10 7 11 2" xfId="2127" xr:uid="{1F8D2215-DDF9-4F58-916D-72B070F64830}"/>
+    <cellStyle name="Comma 10 7 11 3" xfId="1890" xr:uid="{B14BFC47-FAE3-4235-8812-C2B4EC0857A5}"/>
     <cellStyle name="Comma 10 7 12" xfId="522" xr:uid="{5FA176FE-C854-4310-B1AF-013CEA688E8E}"/>
+    <cellStyle name="Comma 10 7 12 2" xfId="2128" xr:uid="{A1F135CA-4971-4370-8CE4-5B61F4A43355}"/>
+    <cellStyle name="Comma 10 7 12 3" xfId="1891" xr:uid="{1A7B607F-B821-44BB-8A91-A66EA5C1CE07}"/>
     <cellStyle name="Comma 10 7 13" xfId="523" xr:uid="{A3222861-B3B9-430A-815B-A6DC5D1C6FC1}"/>
+    <cellStyle name="Comma 10 7 13 2" xfId="2129" xr:uid="{A128E869-733A-48A8-A524-FD2101A1536C}"/>
+    <cellStyle name="Comma 10 7 13 3" xfId="1892" xr:uid="{B5B0FC41-7AFB-442C-9C9D-6A4DC674F3C5}"/>
     <cellStyle name="Comma 10 7 14" xfId="524" xr:uid="{871AFB75-7C34-4291-A50A-156EEB163390}"/>
+    <cellStyle name="Comma 10 7 14 2" xfId="2130" xr:uid="{3F15C088-1173-4B55-9152-BAE37951C5D2}"/>
+    <cellStyle name="Comma 10 7 14 3" xfId="1893" xr:uid="{99508108-614E-4C42-87E0-40AE714A1EB7}"/>
     <cellStyle name="Comma 10 7 15" xfId="525" xr:uid="{99966982-3099-48FA-9C5C-D6D05A27F5CB}"/>
+    <cellStyle name="Comma 10 7 15 2" xfId="2131" xr:uid="{BCB681EC-FB9F-4284-84DC-683A1361EB21}"/>
+    <cellStyle name="Comma 10 7 15 3" xfId="1894" xr:uid="{41575149-B16E-4BA7-BC2F-9F867BDC4F01}"/>
     <cellStyle name="Comma 10 7 16" xfId="526" xr:uid="{675F3E88-4A20-4A14-B79E-B3D7028717AB}"/>
+    <cellStyle name="Comma 10 7 16 2" xfId="2132" xr:uid="{62FD2CC9-C01F-4E64-8230-7E5CC7314CF3}"/>
+    <cellStyle name="Comma 10 7 16 3" xfId="1895" xr:uid="{D64ECA55-914A-4A91-8E2B-9010CDF1C8BC}"/>
     <cellStyle name="Comma 10 7 17" xfId="527" xr:uid="{5A58FFD6-3C01-4A57-ABC4-FD807E21D984}"/>
+    <cellStyle name="Comma 10 7 17 2" xfId="2133" xr:uid="{61A3ABA5-2D69-4F4A-A5B8-C5ADC5998F95}"/>
+    <cellStyle name="Comma 10 7 17 3" xfId="1896" xr:uid="{8DF34781-E083-48C5-B236-C61318A5C2C1}"/>
+    <cellStyle name="Comma 10 7 18" xfId="2125" xr:uid="{45AD55D7-CB1B-4CC6-9F73-8B96369D47B6}"/>
+    <cellStyle name="Comma 10 7 19" xfId="1888" xr:uid="{25EDA739-9DCF-4384-BE9D-7BE08D298EFF}"/>
     <cellStyle name="Comma 10 7 2" xfId="528" xr:uid="{A5CEDC17-3803-4BC7-8FB2-60F697DEDAF6}"/>
+    <cellStyle name="Comma 10 7 2 2" xfId="2134" xr:uid="{426E8292-30A6-4259-AF51-28EAAD4CBEDF}"/>
+    <cellStyle name="Comma 10 7 2 3" xfId="1897" xr:uid="{F9E54C7D-D2FB-4ED6-8A77-180D43BC0874}"/>
     <cellStyle name="Comma 10 7 3" xfId="529" xr:uid="{3801C20C-6BEB-42E4-8D55-1AFA8A987727}"/>
+    <cellStyle name="Comma 10 7 3 2" xfId="2135" xr:uid="{6362E451-2BBB-4328-9D7D-2B6F2BA55C62}"/>
+    <cellStyle name="Comma 10 7 3 3" xfId="1898" xr:uid="{52FA966C-DD62-4E44-BDE5-C820BB3D7F2D}"/>
     <cellStyle name="Comma 10 7 4" xfId="530" xr:uid="{C9FF900A-7299-4E4E-A67D-88C8341D3ECB}"/>
+    <cellStyle name="Comma 10 7 4 2" xfId="2136" xr:uid="{DF9BE74C-CDFF-4B6B-B793-179B475CD24C}"/>
+    <cellStyle name="Comma 10 7 4 3" xfId="1899" xr:uid="{68CBFA46-2830-4631-9EB9-BD60BDFD7C4E}"/>
     <cellStyle name="Comma 10 7 5" xfId="531" xr:uid="{E07E298A-2C94-4551-87E9-47133429E340}"/>
+    <cellStyle name="Comma 10 7 5 2" xfId="2137" xr:uid="{9824EC1F-1AB1-475C-8546-9CDB8CDF0839}"/>
+    <cellStyle name="Comma 10 7 5 3" xfId="1900" xr:uid="{EF853256-A7A2-4C07-A9FB-511FBCCBCAD1}"/>
     <cellStyle name="Comma 10 7 6" xfId="532" xr:uid="{EC8A84AA-544F-428A-AE07-C72677A713F3}"/>
+    <cellStyle name="Comma 10 7 6 2" xfId="2138" xr:uid="{E1927980-3D74-4718-BBBB-2D63C8665E0E}"/>
+    <cellStyle name="Comma 10 7 6 3" xfId="1901" xr:uid="{47DFB486-3BF0-4A84-91A9-DA77FC0DCA17}"/>
     <cellStyle name="Comma 10 7 7" xfId="533" xr:uid="{4D06A793-5EE8-4674-B3F7-A23B1A99BBAA}"/>
+    <cellStyle name="Comma 10 7 7 2" xfId="2139" xr:uid="{053C2178-5541-417A-8806-111CBA61815D}"/>
+    <cellStyle name="Comma 10 7 7 3" xfId="1902" xr:uid="{D88B3D40-A760-44BD-8BC6-D9031B8ECE49}"/>
     <cellStyle name="Comma 10 7 8" xfId="534" xr:uid="{5B9FA7B5-C813-4989-8417-2096B8E0D841}"/>
+    <cellStyle name="Comma 10 7 8 2" xfId="2140" xr:uid="{86459A19-FEDF-4805-86BB-FF0CB3FA68B6}"/>
+    <cellStyle name="Comma 10 7 8 3" xfId="1903" xr:uid="{E30F7B6C-2813-435C-8D55-8E4BB94B032E}"/>
     <cellStyle name="Comma 10 7 9" xfId="535" xr:uid="{132F81CF-EF4A-41FC-B5AF-03C75A93CBD2}"/>
+    <cellStyle name="Comma 10 7 9 2" xfId="2141" xr:uid="{99C9DEF4-1EC3-4497-BDB7-0BC9B964D989}"/>
+    <cellStyle name="Comma 10 7 9 3" xfId="1904" xr:uid="{F2E1DACA-4631-42C2-A9AC-C5E997DD2EB2}"/>
     <cellStyle name="Comma 10 8" xfId="536" xr:uid="{47DB7BB0-E6C5-406E-8DF3-D913CEF61689}"/>
     <cellStyle name="Comma 10 8 10" xfId="537" xr:uid="{A47AA513-61BC-4932-8213-AB80AD83A0C5}"/>
+    <cellStyle name="Comma 10 8 10 2" xfId="2143" xr:uid="{6DB6E7C5-5151-4170-B045-C80CBFDF17EE}"/>
+    <cellStyle name="Comma 10 8 10 3" xfId="1906" xr:uid="{DABA019A-B7F8-431F-AB3E-EE22E986A087}"/>
     <cellStyle name="Comma 10 8 11" xfId="538" xr:uid="{60ECDBD6-5296-4944-BE87-88F59FE9C7F2}"/>
+    <cellStyle name="Comma 10 8 11 2" xfId="2144" xr:uid="{DB3D8AD0-A97D-42DE-AC4D-B29CAE1D1595}"/>
+    <cellStyle name="Comma 10 8 11 3" xfId="1907" xr:uid="{6F0197F0-4DD9-49F5-9368-70031E1F9138}"/>
     <cellStyle name="Comma 10 8 12" xfId="539" xr:uid="{9ED95E99-5896-4092-B973-DDA2A4ABD912}"/>
+    <cellStyle name="Comma 10 8 12 2" xfId="2145" xr:uid="{B303918C-8707-427C-8269-06AB9958699C}"/>
+    <cellStyle name="Comma 10 8 12 3" xfId="1908" xr:uid="{4DF58320-4A2D-49F5-A6F5-2F89E1C41FD2}"/>
     <cellStyle name="Comma 10 8 13" xfId="540" xr:uid="{5B304128-A90F-4B3F-A05C-0A2987894E06}"/>
+    <cellStyle name="Comma 10 8 13 2" xfId="2146" xr:uid="{83CE8444-3E86-4EF9-A89C-25024499DE94}"/>
+    <cellStyle name="Comma 10 8 13 3" xfId="1909" xr:uid="{29825461-480A-4591-90F9-A373AF5F2F5A}"/>
     <cellStyle name="Comma 10 8 14" xfId="541" xr:uid="{D91228C7-4137-41D7-A9DC-9EDCB333BFF8}"/>
+    <cellStyle name="Comma 10 8 14 2" xfId="2147" xr:uid="{B6826DFC-BCD5-4D6A-B21C-103605F9F6C6}"/>
+    <cellStyle name="Comma 10 8 14 3" xfId="1910" xr:uid="{F60CF5A3-F00D-4E37-BAF9-E679ADB901B1}"/>
     <cellStyle name="Comma 10 8 15" xfId="542" xr:uid="{C0700167-5FAA-4408-B46C-946EEE7200AE}"/>
+    <cellStyle name="Comma 10 8 15 2" xfId="2148" xr:uid="{7BC36AE9-9870-45C7-AA4E-553E35D3F3F5}"/>
+    <cellStyle name="Comma 10 8 15 3" xfId="1911" xr:uid="{755AE8A8-D8DA-4473-A1F3-27D8BC71EDAF}"/>
     <cellStyle name="Comma 10 8 16" xfId="543" xr:uid="{D5A3CD1B-A42B-4F0C-ABF5-61F1F01FA17C}"/>
+    <cellStyle name="Comma 10 8 16 2" xfId="2149" xr:uid="{E00606BA-B942-4DD3-9C7A-1591C2F39018}"/>
+    <cellStyle name="Comma 10 8 16 3" xfId="1912" xr:uid="{84A7AA22-6414-46C2-9B38-13C161637DC2}"/>
     <cellStyle name="Comma 10 8 17" xfId="544" xr:uid="{6D15EC6A-4E21-493E-9CF5-93480FCB8718}"/>
+    <cellStyle name="Comma 10 8 17 2" xfId="2150" xr:uid="{66E2BA6F-4827-4EA4-BF72-A3172C28B142}"/>
+    <cellStyle name="Comma 10 8 17 3" xfId="1913" xr:uid="{723BCE00-56EC-4CAD-A427-73056CF119CE}"/>
+    <cellStyle name="Comma 10 8 18" xfId="2142" xr:uid="{44B443D3-6D58-42D8-B613-A2C2FE594376}"/>
+    <cellStyle name="Comma 10 8 19" xfId="1905" xr:uid="{4D3B4E00-16E0-4E69-9552-4541E795A8A7}"/>
     <cellStyle name="Comma 10 8 2" xfId="545" xr:uid="{096E6B6F-35BB-40E1-8E98-D80906051035}"/>
+    <cellStyle name="Comma 10 8 2 2" xfId="2151" xr:uid="{8CF01863-0FC0-4ED0-8584-0BAF5A526EB6}"/>
+    <cellStyle name="Comma 10 8 2 3" xfId="1914" xr:uid="{80BE514B-7138-4168-BCA7-5F9BE60C150B}"/>
     <cellStyle name="Comma 10 8 3" xfId="546" xr:uid="{A6F84871-59F4-45A5-BBC4-3204922871A8}"/>
+    <cellStyle name="Comma 10 8 3 2" xfId="2152" xr:uid="{8ACC193C-DFD9-484A-BFCA-921AAB2B11CB}"/>
+    <cellStyle name="Comma 10 8 3 3" xfId="1915" xr:uid="{2F7F8E06-B567-4258-A04F-355462BF63EE}"/>
     <cellStyle name="Comma 10 8 4" xfId="547" xr:uid="{09DB774A-ED2B-4468-8CD3-3E2DE8D1FCC9}"/>
+    <cellStyle name="Comma 10 8 4 2" xfId="2153" xr:uid="{84AACC0E-C9D9-43B6-A10A-71D9417C945C}"/>
+    <cellStyle name="Comma 10 8 4 3" xfId="1916" xr:uid="{A610DB5B-FFF6-47F9-B003-ED4B0E511BEE}"/>
     <cellStyle name="Comma 10 8 5" xfId="548" xr:uid="{7F0C0819-CD0C-4405-82C2-B640DE733873}"/>
+    <cellStyle name="Comma 10 8 5 2" xfId="2154" xr:uid="{335007CB-4FC8-4447-B0E1-6C1AEAECB96F}"/>
+    <cellStyle name="Comma 10 8 5 3" xfId="1917" xr:uid="{A6C7A698-0E34-4519-92BE-E643F9A165CA}"/>
     <cellStyle name="Comma 10 8 6" xfId="549" xr:uid="{AA0D416C-19A6-4C23-B110-24C6343E1FF4}"/>
+    <cellStyle name="Comma 10 8 6 2" xfId="2155" xr:uid="{ACDB35DD-241A-4F28-9B5D-2B1F67C2FA3A}"/>
+    <cellStyle name="Comma 10 8 6 3" xfId="1918" xr:uid="{1B2C1865-E2AD-4B30-8E34-7C6CAA636D9F}"/>
     <cellStyle name="Comma 10 8 7" xfId="550" xr:uid="{88BE2F73-E400-416E-9F6C-A659922A4498}"/>
+    <cellStyle name="Comma 10 8 7 2" xfId="2156" xr:uid="{8107A8AB-D19E-4077-8401-F50A51DFD94C}"/>
+    <cellStyle name="Comma 10 8 7 3" xfId="1919" xr:uid="{15D16816-91A2-49F0-8738-82E4772C015A}"/>
     <cellStyle name="Comma 10 8 8" xfId="551" xr:uid="{8097CBFB-7025-41F2-A6A8-5195FC852A1F}"/>
+    <cellStyle name="Comma 10 8 8 2" xfId="2157" xr:uid="{9F9567E1-C0A3-4072-A7F9-2A3BF9BB46ED}"/>
+    <cellStyle name="Comma 10 8 8 3" xfId="1920" xr:uid="{5D80F678-ED83-45B0-A6D4-DB562AE2D08E}"/>
     <cellStyle name="Comma 10 8 9" xfId="552" xr:uid="{ADF47313-4EEB-493B-ACC2-3437B72E0367}"/>
+    <cellStyle name="Comma 10 8 9 2" xfId="2158" xr:uid="{59FED4AD-FD73-4D15-AEAC-EB7C7713E099}"/>
+    <cellStyle name="Comma 10 8 9 3" xfId="1921" xr:uid="{1B4BA111-4D28-4328-A3C9-79597B6E8EFC}"/>
+    <cellStyle name="Comma 10 9" xfId="2039" xr:uid="{245526B1-8A40-4889-8160-D2EE95E9A214}"/>
     <cellStyle name="Comma 11" xfId="553" xr:uid="{6ED9277F-BCC7-4A98-9950-9A9AAFC0BB65}"/>
+    <cellStyle name="Comma 11 2" xfId="2159" xr:uid="{1DE5851E-C48F-47D6-9A05-EBA8237E407A}"/>
+    <cellStyle name="Comma 11 3" xfId="1922" xr:uid="{2FEA01C9-54DD-4799-8317-5C2B80CD1D99}"/>
     <cellStyle name="Comma 12" xfId="554" xr:uid="{20291982-5470-4419-8C91-39BD97290E17}"/>
+    <cellStyle name="Comma 12 2" xfId="2160" xr:uid="{95868716-AF71-4360-A17C-6CBE611AE986}"/>
+    <cellStyle name="Comma 12 3" xfId="1923" xr:uid="{ADDA1EA4-9E37-4733-A6EC-603A31246313}"/>
     <cellStyle name="Comma 13" xfId="555" xr:uid="{7B7B469D-149B-454B-B48A-5D949BD77C35}"/>
+    <cellStyle name="Comma 13 2" xfId="2161" xr:uid="{FE7BAA3B-1AC9-4A1B-AE82-5F39159B8AEC}"/>
+    <cellStyle name="Comma 13 3" xfId="1924" xr:uid="{2603F62B-8AE8-4F8B-898C-9BB50B7E312D}"/>
     <cellStyle name="Comma 14" xfId="556" xr:uid="{B41743E9-1E56-400A-8006-2D4A684636F3}"/>
+    <cellStyle name="Comma 14 2" xfId="2162" xr:uid="{C0090B2E-5829-40DA-91FF-7182441F3308}"/>
+    <cellStyle name="Comma 14 3" xfId="1925" xr:uid="{48190608-9BF9-4FED-859A-760C4BC5C59F}"/>
     <cellStyle name="Comma 15" xfId="557" xr:uid="{7C4969F5-5321-471E-AD41-7290D0C548E6}"/>
+    <cellStyle name="Comma 15 2" xfId="2163" xr:uid="{E3E6F1CC-02FC-4549-9F73-327DB5B313D8}"/>
+    <cellStyle name="Comma 15 3" xfId="1926" xr:uid="{9C55ADCE-9AEF-48B5-847B-C914BE12027C}"/>
     <cellStyle name="Comma 16" xfId="558" xr:uid="{DF266CD4-77EA-492D-B0C2-BABF85179EBC}"/>
+    <cellStyle name="Comma 16 2" xfId="2164" xr:uid="{1801C0F0-FFC3-4433-87C5-5DA1151432E9}"/>
+    <cellStyle name="Comma 16 3" xfId="1927" xr:uid="{819BAFC1-BF73-4113-852F-1322FFBCEE80}"/>
     <cellStyle name="Comma 17" xfId="559" xr:uid="{252D2CEE-508B-4956-BD28-D57F91990CA3}"/>
+    <cellStyle name="Comma 17 2" xfId="2165" xr:uid="{C921FD3C-54E8-491E-ABF7-FF78513DDFAB}"/>
+    <cellStyle name="Comma 17 3" xfId="1928" xr:uid="{FFB9C011-3DFC-49F7-992B-02C7294D1612}"/>
     <cellStyle name="Comma 18" xfId="560" xr:uid="{56849552-EE1C-48CE-9524-F664EA973A32}"/>
+    <cellStyle name="Comma 18 2" xfId="2166" xr:uid="{95EB28F1-9491-4861-B21B-2A29C906CEC6}"/>
+    <cellStyle name="Comma 18 3" xfId="1929" xr:uid="{670F14A0-0701-488A-AD26-C37646D84D54}"/>
     <cellStyle name="Comma 19" xfId="561" xr:uid="{B26C2ADC-EC02-4454-9ED2-7FF226137FDF}"/>
+    <cellStyle name="Comma 19 2" xfId="2167" xr:uid="{A1E67DE9-9EA2-4BFB-AE3B-DDA80CCC98DC}"/>
+    <cellStyle name="Comma 19 3" xfId="1930" xr:uid="{DDD7A0C9-D06E-4FC0-8C74-F16429F252E6}"/>
     <cellStyle name="Comma 2" xfId="562" xr:uid="{AC552860-7111-4BDC-9DD2-9C1D720EB3D0}"/>
     <cellStyle name="Comma 2 10" xfId="563" xr:uid="{38F8C41D-3BA2-4127-BBDC-058D8BDF77FF}"/>
     <cellStyle name="Comma 2 11" xfId="564" xr:uid="{AB6E544B-2BE0-4528-BE3B-C3E99A94AFE3}"/>
@@ -3874,20 +4624,48 @@
     <cellStyle name="Comma 2 15" xfId="568" xr:uid="{B09397A0-2B5D-4D5B-85CA-417678BBE554}"/>
     <cellStyle name="Comma 2 16" xfId="569" xr:uid="{F255443B-1CC5-46D4-A18E-9703210442E6}"/>
     <cellStyle name="Comma 2 17" xfId="570" xr:uid="{1C8B144A-22C7-4771-8C72-998299C92D79}"/>
+    <cellStyle name="Comma 2 17 2" xfId="2169" xr:uid="{2B0AB1A6-734B-4558-B556-E5DE070598CE}"/>
+    <cellStyle name="Comma 2 17 3" xfId="1932" xr:uid="{E513A679-5AAE-4FBE-8769-1475FD6EEECD}"/>
     <cellStyle name="Comma 2 18" xfId="571" xr:uid="{E220744C-FEC4-4361-BA20-23B01900E887}"/>
+    <cellStyle name="Comma 2 18 2" xfId="2170" xr:uid="{17FCF6E4-C48E-45C1-8386-AC9D99862855}"/>
+    <cellStyle name="Comma 2 18 3" xfId="1933" xr:uid="{4C61C190-1C4F-49B1-9323-FEBC193E13F4}"/>
     <cellStyle name="Comma 2 19" xfId="572" xr:uid="{4A8A1607-9003-4EA6-987D-E2FA4AAF12C0}"/>
     <cellStyle name="Comma 2 19 2" xfId="573" xr:uid="{AA79411B-CA8F-4194-9F4A-28EFE9D156E7}"/>
+    <cellStyle name="Comma 2 19 2 2" xfId="2172" xr:uid="{34A9D865-7992-49F4-99B9-0406929B97DB}"/>
+    <cellStyle name="Comma 2 19 2 3" xfId="1935" xr:uid="{F7C65482-FB8F-4BBE-AF9A-E2BBD54EAA25}"/>
     <cellStyle name="Comma 2 19 3" xfId="574" xr:uid="{905A7EEE-F2B0-4368-9D8C-F7FDA40A6A65}"/>
+    <cellStyle name="Comma 2 19 3 2" xfId="2173" xr:uid="{6DEE84A4-4974-41CD-A6CC-A20A83BC6A87}"/>
+    <cellStyle name="Comma 2 19 3 3" xfId="1936" xr:uid="{B6E31C1E-ED02-46EF-8E53-0F805FD7C0F4}"/>
+    <cellStyle name="Comma 2 19 4" xfId="2171" xr:uid="{2F3972B6-0464-4B0A-8E79-E4DF3D15942A}"/>
+    <cellStyle name="Comma 2 19 5" xfId="1934" xr:uid="{D484292C-9267-41AD-95E0-CB655B189224}"/>
     <cellStyle name="Comma 2 2" xfId="575" xr:uid="{791A6D5D-A814-419E-A98E-6F223F4BA9C4}"/>
     <cellStyle name="Comma 2 2 2" xfId="576" xr:uid="{42928FFF-DF65-45E9-9DE0-E3FBFFA08446}"/>
     <cellStyle name="Comma 2 2 3" xfId="577" xr:uid="{ECE82881-EB4F-438C-A780-0CDF0C5BD90D}"/>
+    <cellStyle name="Comma 2 2 3 2" xfId="2175" xr:uid="{52126050-98D2-43A6-B4D0-B81F10D056B3}"/>
+    <cellStyle name="Comma 2 2 3 3" xfId="1938" xr:uid="{C82D3B19-928B-42FC-87A5-F2388D62A77D}"/>
     <cellStyle name="Comma 2 2 4" xfId="578" xr:uid="{6FAC4DCD-0A25-4866-A24D-E31A4DC94ECB}"/>
+    <cellStyle name="Comma 2 2 4 2" xfId="2176" xr:uid="{3C9C810E-517A-4965-B272-44DBDA643CD7}"/>
+    <cellStyle name="Comma 2 2 4 3" xfId="1939" xr:uid="{ECE07F31-5501-4DF7-9A69-5EF8AF366D69}"/>
     <cellStyle name="Comma 2 2 5" xfId="579" xr:uid="{DD03CFA0-B2B2-493C-89D5-A085586CE85F}"/>
+    <cellStyle name="Comma 2 2 5 2" xfId="2177" xr:uid="{853A8B0B-8559-433F-93B2-DA0B34E08797}"/>
+    <cellStyle name="Comma 2 2 5 3" xfId="1940" xr:uid="{1161390D-0470-4602-A181-61428EBF6127}"/>
+    <cellStyle name="Comma 2 2 6" xfId="2174" xr:uid="{C1745283-547C-4F1E-B5C7-CFC9F6681C30}"/>
+    <cellStyle name="Comma 2 2 7" xfId="1937" xr:uid="{38E8F477-1D6B-490F-BC07-4C34A7D5B3F8}"/>
     <cellStyle name="Comma 2 20" xfId="580" xr:uid="{F276E7BA-3636-4F64-A7A7-0E94D9E3B088}"/>
+    <cellStyle name="Comma 2 20 2" xfId="2178" xr:uid="{0426A4B7-1F88-44D4-9B56-F14081CB6657}"/>
+    <cellStyle name="Comma 2 20 3" xfId="1941" xr:uid="{D2EB137F-DCED-453C-9A23-FF34D74BEED6}"/>
     <cellStyle name="Comma 2 21" xfId="581" xr:uid="{105F14C6-90DC-47E4-A8FD-40400B14CAD6}"/>
+    <cellStyle name="Comma 2 21 2" xfId="2179" xr:uid="{0CE0FD85-50C2-419E-AB7A-5734BB10CB8B}"/>
+    <cellStyle name="Comma 2 21 3" xfId="1942" xr:uid="{765B5CD3-43FC-47D6-910E-1E04FA22E23C}"/>
+    <cellStyle name="Comma 2 22" xfId="2168" xr:uid="{7ADF1BCD-FAA1-40AE-9C18-B91CB8674611}"/>
+    <cellStyle name="Comma 2 23" xfId="1931" xr:uid="{74E8DFAD-F0D6-48FA-AD91-DBE98B6F3806}"/>
     <cellStyle name="Comma 2 3" xfId="582" xr:uid="{29F9D515-2DCF-4A8B-A787-9F7067EC5626}"/>
     <cellStyle name="Comma 2 3 2" xfId="583" xr:uid="{FB4ECDD0-B420-4702-BDB0-9E352928944E}"/>
+    <cellStyle name="Comma 2 3 2 2" xfId="2180" xr:uid="{4E858377-A6DF-48C9-B257-78ADBC1CA928}"/>
+    <cellStyle name="Comma 2 3 2 3" xfId="1943" xr:uid="{FB69246C-CD3C-47C4-867C-92ED8780AEE9}"/>
     <cellStyle name="Comma 2 3 3" xfId="584" xr:uid="{784271BA-BD5A-445C-902B-5624008F128A}"/>
+    <cellStyle name="Comma 2 3 3 2" xfId="2181" xr:uid="{7BBFBCA2-244A-454A-BAF0-BE957D503561}"/>
+    <cellStyle name="Comma 2 3 3 3" xfId="1944" xr:uid="{206B7B9A-0742-432A-A99A-F3BC05EF5268}"/>
     <cellStyle name="Comma 2 4" xfId="585" xr:uid="{336CE588-9659-4619-98A9-C20ED5F0D1F5}"/>
     <cellStyle name="Comma 2 5" xfId="586" xr:uid="{57E8BC09-5E53-4153-BFD0-B33AA487BFD6}"/>
     <cellStyle name="Comma 2 6" xfId="587" xr:uid="{E0FF3BBF-E07A-44A0-921B-E11A4DD4FD1D}"/>
@@ -3896,91 +4674,261 @@
     <cellStyle name="Comma 2 9" xfId="590" xr:uid="{6CC191D8-3D4F-4C8E-A21F-945292A11C53}"/>
     <cellStyle name="Comma 3" xfId="591" xr:uid="{EFF3A942-D02A-46FF-8CC7-C0150BDEA4F0}"/>
     <cellStyle name="Comma 3 10" xfId="592" xr:uid="{4D8387C8-160A-400D-975A-4B0A7845F3BB}"/>
+    <cellStyle name="Comma 3 10 2" xfId="2183" xr:uid="{7A215495-754A-4579-8D38-1AC5E1829E0E}"/>
+    <cellStyle name="Comma 3 10 3" xfId="1946" xr:uid="{65EA1C06-C921-469B-A616-14BF4602D331}"/>
+    <cellStyle name="Comma 3 11" xfId="2182" xr:uid="{576B88AB-862E-4121-9115-FAA899B3915C}"/>
+    <cellStyle name="Comma 3 12" xfId="1945" xr:uid="{772DF2E5-F911-4700-A47D-238B21043099}"/>
     <cellStyle name="Comma 3 2" xfId="593" xr:uid="{5FAC27B3-C8FE-4168-AF27-ACADC521DF41}"/>
+    <cellStyle name="Comma 3 2 2" xfId="2184" xr:uid="{E2FCCEF1-32E4-4DC8-AABF-4CB547E819A7}"/>
+    <cellStyle name="Comma 3 2 3" xfId="1947" xr:uid="{EF597438-F98A-4825-9810-C44468F32D11}"/>
     <cellStyle name="Comma 3 3" xfId="594" xr:uid="{F96616C1-F318-4096-A6FF-36BD670B3752}"/>
+    <cellStyle name="Comma 3 3 2" xfId="2185" xr:uid="{BA58B95C-AD76-44C7-8B5D-199030794860}"/>
+    <cellStyle name="Comma 3 3 3" xfId="1948" xr:uid="{13228960-07D9-4911-BDD9-11C4DD075954}"/>
     <cellStyle name="Comma 3 4" xfId="595" xr:uid="{8A05A387-8A4C-4A75-A1B8-EE6646BB7376}"/>
+    <cellStyle name="Comma 3 4 2" xfId="2186" xr:uid="{DB494038-7E71-47FF-ADC8-65DB967BFC90}"/>
+    <cellStyle name="Comma 3 4 3" xfId="1949" xr:uid="{D90CCB21-0F46-4D9C-B37C-14164458408F}"/>
     <cellStyle name="Comma 3 5" xfId="596" xr:uid="{FF1F7B80-E8E0-4BC5-91E6-29BB41F191D1}"/>
+    <cellStyle name="Comma 3 5 2" xfId="2187" xr:uid="{F74FC952-D97F-4E89-97B6-FEF4329E972C}"/>
+    <cellStyle name="Comma 3 5 3" xfId="1950" xr:uid="{97C15407-C43A-4198-9D7C-47CDC330BA2E}"/>
     <cellStyle name="Comma 3 6" xfId="597" xr:uid="{9680860D-0AC4-49F7-AE4D-78BBE5C00956}"/>
+    <cellStyle name="Comma 3 6 2" xfId="2188" xr:uid="{0E527849-2230-4015-B6A2-CBD005AFCD6B}"/>
+    <cellStyle name="Comma 3 6 3" xfId="1951" xr:uid="{31CEDFCE-6596-4EA5-A757-68772984ED99}"/>
     <cellStyle name="Comma 3 7" xfId="598" xr:uid="{6306D39D-E1A9-4475-8C22-AB853AFD14D8}"/>
+    <cellStyle name="Comma 3 7 2" xfId="2189" xr:uid="{1601193B-8143-41EE-91B0-18BDB765502F}"/>
+    <cellStyle name="Comma 3 7 3" xfId="1952" xr:uid="{148B94DD-A2CE-4C05-88D3-6B4E6DA5B833}"/>
     <cellStyle name="Comma 3 8" xfId="599" xr:uid="{57ED7A54-59EF-423D-AEC5-1E3BA35EAAA6}"/>
+    <cellStyle name="Comma 3 8 2" xfId="2190" xr:uid="{47F76D0A-B42E-4B3D-A92D-6775F5F307BC}"/>
+    <cellStyle name="Comma 3 8 3" xfId="1953" xr:uid="{5F8B9FF1-8BB0-4D7A-B90A-A7F79800EDFF}"/>
     <cellStyle name="Comma 3 9" xfId="600" xr:uid="{8735F7C5-F78C-4F27-8F0C-52F08FF39F82}"/>
+    <cellStyle name="Comma 3 9 2" xfId="2191" xr:uid="{4DBDBFD1-00B8-4BEA-9C6F-B1CCB6EB4EBD}"/>
+    <cellStyle name="Comma 3 9 3" xfId="1954" xr:uid="{B7D98BFC-0E34-4EBD-8AFA-0396122A8320}"/>
     <cellStyle name="Comma 4" xfId="601" xr:uid="{666EA9D4-D283-429B-9972-1AF34CCB33D2}"/>
+    <cellStyle name="Comma 4 10" xfId="2192" xr:uid="{80A9C388-010D-45A4-86E7-FD7EF096C6DA}"/>
+    <cellStyle name="Comma 4 11" xfId="1955" xr:uid="{5DFF0C1E-AD38-4884-B5D8-668F903C180E}"/>
     <cellStyle name="Comma 4 2" xfId="602" xr:uid="{10483DF6-CD32-4ED0-8AA5-780EEFB60249}"/>
+    <cellStyle name="Comma 4 2 2" xfId="2193" xr:uid="{781DB80C-66F9-40B6-B14D-179452CE1A15}"/>
+    <cellStyle name="Comma 4 2 3" xfId="1956" xr:uid="{134C0CEC-3365-4E00-8E92-B28C9F622611}"/>
     <cellStyle name="Comma 4 3" xfId="603" xr:uid="{EEC669A4-B0AA-4FB6-8C03-B65A731EDC83}"/>
+    <cellStyle name="Comma 4 3 2" xfId="2194" xr:uid="{708E012B-508C-40E0-B0BB-EBC728CAA76B}"/>
+    <cellStyle name="Comma 4 3 3" xfId="1957" xr:uid="{B3C096C7-0092-4973-9BD3-EBEA977E1D14}"/>
     <cellStyle name="Comma 4 4" xfId="604" xr:uid="{D3E40562-3486-4378-A09F-2E3C5E135CD2}"/>
+    <cellStyle name="Comma 4 4 2" xfId="2195" xr:uid="{6741778C-15A3-4507-BC49-1F9E981A5EB2}"/>
+    <cellStyle name="Comma 4 4 3" xfId="1958" xr:uid="{73FCA3D8-DAC3-4749-9835-010E76CFF517}"/>
     <cellStyle name="Comma 4 5" xfId="605" xr:uid="{F57AEBE4-4526-496E-87D8-8202C753369E}"/>
+    <cellStyle name="Comma 4 5 2" xfId="2196" xr:uid="{CB9CDA60-9484-4EC4-B9AB-D3562B79A873}"/>
+    <cellStyle name="Comma 4 5 3" xfId="1959" xr:uid="{AE0B9B91-1FB5-44D6-A7D3-7047CA592413}"/>
     <cellStyle name="Comma 4 6" xfId="606" xr:uid="{AE69E325-89E3-41AD-B763-9E79A4898F22}"/>
+    <cellStyle name="Comma 4 6 2" xfId="2197" xr:uid="{5154F3B5-7ACC-45FF-A9B5-652505825845}"/>
+    <cellStyle name="Comma 4 6 3" xfId="1960" xr:uid="{E41745C0-F6FC-4DBB-AB3E-7D8C142EE02C}"/>
     <cellStyle name="Comma 4 7" xfId="607" xr:uid="{62701780-9F0B-4E6B-AE51-0E0D2412F5C5}"/>
+    <cellStyle name="Comma 4 7 2" xfId="2198" xr:uid="{F082F9DC-D327-457E-8682-82F51A27338F}"/>
+    <cellStyle name="Comma 4 7 3" xfId="1961" xr:uid="{C87A52F3-E2B4-4E4C-A6A1-583EB3129A6D}"/>
     <cellStyle name="Comma 4 8" xfId="608" xr:uid="{4CB912CB-2AA9-4F05-9D9B-5A5079B2C25F}"/>
+    <cellStyle name="Comma 4 8 2" xfId="2199" xr:uid="{ED9740AC-1440-4C45-9465-B779AA229D93}"/>
+    <cellStyle name="Comma 4 8 3" xfId="1962" xr:uid="{58D3DE90-2D10-4154-A94D-97692EAB3AA7}"/>
     <cellStyle name="Comma 4 9" xfId="609" xr:uid="{0AD6F7A0-7063-4F73-B076-9B9A51396E07}"/>
+    <cellStyle name="Comma 4 9 2" xfId="2200" xr:uid="{EF675F62-FCDA-40BD-8D95-B596705F875A}"/>
+    <cellStyle name="Comma 4 9 3" xfId="1963" xr:uid="{3F3F750F-D981-430D-8683-F47F4A658910}"/>
     <cellStyle name="Comma 5" xfId="610" xr:uid="{91E8D148-3BCC-4CCF-9736-F7A80A1B8A1A}"/>
+    <cellStyle name="Comma 5 10" xfId="1964" xr:uid="{C09DA466-6891-40CA-A8AB-16E5D6C394C6}"/>
     <cellStyle name="Comma 5 2" xfId="611" xr:uid="{9B12E61B-9B1B-43BF-9C33-C1D6B3ACB9D0}"/>
+    <cellStyle name="Comma 5 2 2" xfId="2202" xr:uid="{034373F0-3B31-4B24-AFD8-1363505B1857}"/>
+    <cellStyle name="Comma 5 2 3" xfId="1965" xr:uid="{C0CE0AB4-0446-4AFD-860F-1AB3CAEC96A3}"/>
     <cellStyle name="Comma 5 3" xfId="612" xr:uid="{9D34FEE0-DD43-4B89-8C29-33ADA356C933}"/>
+    <cellStyle name="Comma 5 3 2" xfId="2203" xr:uid="{FFDFE46C-8623-4688-97CA-183C16926691}"/>
+    <cellStyle name="Comma 5 3 3" xfId="1966" xr:uid="{B381F5ED-6B99-4748-A0B6-60B0436E43EC}"/>
     <cellStyle name="Comma 5 4" xfId="613" xr:uid="{77B6F1E2-FF9C-4FEA-B01C-E190725643E2}"/>
+    <cellStyle name="Comma 5 4 2" xfId="2204" xr:uid="{C6569081-10BB-4292-B1B7-0081D2602329}"/>
+    <cellStyle name="Comma 5 4 3" xfId="1967" xr:uid="{DB37B89B-9BD1-4B7D-B217-96995143D38A}"/>
     <cellStyle name="Comma 5 5" xfId="614" xr:uid="{AB6FC711-D840-449B-884E-CE17DF7A5892}"/>
+    <cellStyle name="Comma 5 5 2" xfId="2205" xr:uid="{EAFDC8BC-3A6A-4AFB-A294-06C89B107555}"/>
+    <cellStyle name="Comma 5 5 3" xfId="1968" xr:uid="{4DFBA935-E3E2-4597-A4DE-E2A8D0365F75}"/>
     <cellStyle name="Comma 5 6" xfId="615" xr:uid="{FAD05973-B586-441F-8EA4-DFBF3124F2F1}"/>
+    <cellStyle name="Comma 5 6 2" xfId="2206" xr:uid="{EE8AB80C-8114-4AC0-A74D-CEDC7D8E0981}"/>
+    <cellStyle name="Comma 5 6 3" xfId="1969" xr:uid="{CEDA6920-79D0-4C9D-B60D-AF031612A5E3}"/>
     <cellStyle name="Comma 5 7" xfId="616" xr:uid="{54BD4258-6A73-4A71-BA28-520B9DA62026}"/>
+    <cellStyle name="Comma 5 7 2" xfId="2207" xr:uid="{B16EF145-912C-420D-937F-4CE578058215}"/>
+    <cellStyle name="Comma 5 7 3" xfId="1970" xr:uid="{5D945E59-10D7-4E9B-8D8B-9BB747F5AEE7}"/>
     <cellStyle name="Comma 5 8" xfId="617" xr:uid="{618E9AE7-FB4F-4D66-BB74-10B9ABBDF81D}"/>
+    <cellStyle name="Comma 5 8 2" xfId="2208" xr:uid="{4DAB0E9C-79FE-4492-9CA3-1D4E31EEEB10}"/>
+    <cellStyle name="Comma 5 8 3" xfId="1971" xr:uid="{77354AA3-45FE-467F-AB00-9977ED9FE0FE}"/>
+    <cellStyle name="Comma 5 9" xfId="2201" xr:uid="{AD23828E-A944-4C55-9B8B-F9F7819F6538}"/>
     <cellStyle name="Comma 6" xfId="618" xr:uid="{3100EA3B-12EE-4D41-94A0-CD3BFECE7C2D}"/>
+    <cellStyle name="Comma 6 10" xfId="1972" xr:uid="{F09EAA43-D908-4F5F-97BF-8AAA1419C96E}"/>
     <cellStyle name="Comma 6 2" xfId="619" xr:uid="{6008823A-6A05-4BE2-9AB1-2ACCF0B200BF}"/>
+    <cellStyle name="Comma 6 2 2" xfId="2210" xr:uid="{169E48D6-2A83-4FF3-B62E-3EEDE8E2BD01}"/>
+    <cellStyle name="Comma 6 2 3" xfId="1973" xr:uid="{A4617EDC-9AC9-46E2-A3E1-238A4D7387BC}"/>
     <cellStyle name="Comma 6 3" xfId="620" xr:uid="{739CCFF1-AEC8-4C20-A82B-E888B0C3327E}"/>
+    <cellStyle name="Comma 6 3 2" xfId="2211" xr:uid="{5C962774-078A-40BA-9415-8DD3B43BE36F}"/>
+    <cellStyle name="Comma 6 3 3" xfId="1974" xr:uid="{7AB35C51-2B82-4EFA-B864-7D3F812F610F}"/>
     <cellStyle name="Comma 6 4" xfId="621" xr:uid="{6ECC49F5-6C67-41F9-AAA2-3C6B43421EA0}"/>
+    <cellStyle name="Comma 6 4 2" xfId="2212" xr:uid="{1280D076-099C-4C0C-95FA-DE713254632C}"/>
+    <cellStyle name="Comma 6 4 3" xfId="1975" xr:uid="{F29429CD-8852-4EF8-A450-DA0849938D6B}"/>
     <cellStyle name="Comma 6 5" xfId="622" xr:uid="{91D105CA-B1BA-4E56-AECB-01F32114C9A3}"/>
+    <cellStyle name="Comma 6 5 2" xfId="2213" xr:uid="{CB9A40D2-2CA3-49A5-9B84-DF441567B4D0}"/>
+    <cellStyle name="Comma 6 5 3" xfId="1976" xr:uid="{BB504364-11BC-4D66-B33F-63A54DCB8058}"/>
     <cellStyle name="Comma 6 6" xfId="623" xr:uid="{07D14574-438D-4E84-8B1F-AAAD56F44823}"/>
+    <cellStyle name="Comma 6 6 2" xfId="2214" xr:uid="{33CB8AAE-FCBB-403A-A8A6-12FC9B2460C3}"/>
+    <cellStyle name="Comma 6 6 3" xfId="1977" xr:uid="{772524B3-3EDD-4248-BBFF-5619F348A82A}"/>
     <cellStyle name="Comma 6 7" xfId="624" xr:uid="{DB04328A-7A68-4101-9694-1CEEC051CB0C}"/>
+    <cellStyle name="Comma 6 7 2" xfId="2215" xr:uid="{C9821B55-5C77-4B74-AE12-AB886009B925}"/>
+    <cellStyle name="Comma 6 7 3" xfId="1978" xr:uid="{7F257002-592E-46E1-9102-4250C20F901C}"/>
     <cellStyle name="Comma 6 8" xfId="625" xr:uid="{CC367ED2-08DC-4BF3-9304-684617D67631}"/>
+    <cellStyle name="Comma 6 8 2" xfId="2216" xr:uid="{8DD889D6-F3BF-48FE-B02E-AF43316C98DA}"/>
+    <cellStyle name="Comma 6 8 3" xfId="1979" xr:uid="{1D1412D6-A227-4CD0-90B3-EEFAA2FA51AB}"/>
+    <cellStyle name="Comma 6 9" xfId="2209" xr:uid="{5EAE3762-DAB8-4F4D-BB64-22785F8F5521}"/>
     <cellStyle name="Comma 7" xfId="626" xr:uid="{320B562B-1DA9-4E2C-99CB-0F603F45105F}"/>
     <cellStyle name="Comma 7 10" xfId="627" xr:uid="{F4F0E5D0-FC7A-45E8-8CB2-590130A3F825}"/>
+    <cellStyle name="Comma 7 10 2" xfId="2217" xr:uid="{D03DE012-F3F6-4F46-B465-0EC2FF83DFDA}"/>
+    <cellStyle name="Comma 7 10 3" xfId="1980" xr:uid="{366EAA14-0D9C-4766-8D05-ABFF63A35A09}"/>
     <cellStyle name="Comma 7 11" xfId="628" xr:uid="{7C89DA23-7816-41B9-A44B-DF274C7A6FDC}"/>
+    <cellStyle name="Comma 7 11 2" xfId="2218" xr:uid="{4B1CEFB3-C8F6-4D6E-A603-218715FC3016}"/>
+    <cellStyle name="Comma 7 11 3" xfId="1981" xr:uid="{FC7367A7-277A-43C4-BECE-4408E75507FB}"/>
     <cellStyle name="Comma 7 12" xfId="629" xr:uid="{A8988E15-C663-4014-8382-0F59A05E585A}"/>
+    <cellStyle name="Comma 7 12 2" xfId="2219" xr:uid="{B9E3D40B-1C01-4DC7-A169-FE618718EC60}"/>
+    <cellStyle name="Comma 7 12 3" xfId="1982" xr:uid="{1766A3FC-6DC1-4EC7-88F1-983BEBF3E386}"/>
     <cellStyle name="Comma 7 13" xfId="630" xr:uid="{61DB1C80-C38D-47E4-A859-D993D429DFAC}"/>
+    <cellStyle name="Comma 7 13 2" xfId="2220" xr:uid="{BFDA9108-09FC-4C3D-8218-FB40B54BE9A0}"/>
+    <cellStyle name="Comma 7 13 3" xfId="1983" xr:uid="{5D92073D-F386-4096-9588-723735728931}"/>
     <cellStyle name="Comma 7 14" xfId="631" xr:uid="{F0946BEC-713C-4CE6-BD40-FD4880E903F7}"/>
+    <cellStyle name="Comma 7 14 2" xfId="2221" xr:uid="{1F0142E8-9EA3-4654-84C6-967F6F6540EC}"/>
+    <cellStyle name="Comma 7 14 3" xfId="1984" xr:uid="{D77D318E-41CE-4D44-80B0-08A7C19A0415}"/>
     <cellStyle name="Comma 7 15" xfId="632" xr:uid="{816B57A7-809B-4179-BB01-73A197F2AB3E}"/>
+    <cellStyle name="Comma 7 15 2" xfId="2222" xr:uid="{B5384471-D134-4D58-B3BB-333D6E641BD2}"/>
+    <cellStyle name="Comma 7 15 3" xfId="1985" xr:uid="{BE482EBA-6927-40B8-8EE1-ED4FF2F73A60}"/>
     <cellStyle name="Comma 7 16" xfId="633" xr:uid="{2AFEA77C-8FF3-4235-9412-FA37FDC94DFE}"/>
+    <cellStyle name="Comma 7 16 2" xfId="2223" xr:uid="{3EB93686-98E8-4D7F-9DD6-5750A694000D}"/>
+    <cellStyle name="Comma 7 16 3" xfId="1986" xr:uid="{F19F9334-FB4B-4DAC-A403-3912383ECDCC}"/>
     <cellStyle name="Comma 7 17" xfId="634" xr:uid="{08029A13-BEAD-46CF-BCBF-D492593D323B}"/>
+    <cellStyle name="Comma 7 17 2" xfId="2224" xr:uid="{D767C2C4-5514-48A2-89D5-968BC19A7E18}"/>
+    <cellStyle name="Comma 7 17 3" xfId="1987" xr:uid="{2E649FA6-0701-4248-B26A-2B555472097C}"/>
     <cellStyle name="Comma 7 18" xfId="635" xr:uid="{C4490ABF-0F18-4800-BC9E-F665195DCA51}"/>
+    <cellStyle name="Comma 7 18 2" xfId="2225" xr:uid="{C9E8022F-F78C-4D0E-9320-CC890BB1B3F2}"/>
+    <cellStyle name="Comma 7 18 3" xfId="1988" xr:uid="{2728811D-16A3-45A9-89B6-BE3BFB933284}"/>
     <cellStyle name="Comma 7 19" xfId="636" xr:uid="{D546E899-420B-4F21-99F5-E5DDB8B041FE}"/>
+    <cellStyle name="Comma 7 19 2" xfId="2226" xr:uid="{4250E4BD-EF6E-40CF-9D65-440F98A7B549}"/>
+    <cellStyle name="Comma 7 19 3" xfId="1989" xr:uid="{DFE0D573-CBD6-4AD8-8205-1A531068A9B2}"/>
     <cellStyle name="Comma 7 2" xfId="637" xr:uid="{B3627C25-2441-4CF1-B4D4-456EB8E56CE1}"/>
+    <cellStyle name="Comma 7 2 2" xfId="2227" xr:uid="{D5AB2C7A-61AC-4075-88D4-20F010CE4D35}"/>
+    <cellStyle name="Comma 7 2 3" xfId="1990" xr:uid="{19842667-FB70-41A5-AA9F-84D7AB9F4085}"/>
     <cellStyle name="Comma 7 20" xfId="638" xr:uid="{783A5BA3-67BB-4476-BD48-AE4FD8A8F924}"/>
+    <cellStyle name="Comma 7 20 2" xfId="2228" xr:uid="{00DB15CE-6061-4620-96E8-97A3A2719A9B}"/>
+    <cellStyle name="Comma 7 20 3" xfId="1991" xr:uid="{FDD651CB-7F38-4460-B422-FE37C2470C3A}"/>
     <cellStyle name="Comma 7 21" xfId="639" xr:uid="{0596DA76-A6D5-4908-AE2A-A86D868F6241}"/>
+    <cellStyle name="Comma 7 21 2" xfId="2229" xr:uid="{4DF6A704-1500-41F8-858F-45B52AE13DFE}"/>
+    <cellStyle name="Comma 7 21 3" xfId="1992" xr:uid="{6F8488CE-7657-4752-8ABD-E0DC7467854C}"/>
     <cellStyle name="Comma 7 3" xfId="640" xr:uid="{94B28D04-0799-4F43-9231-44F2F443610B}"/>
     <cellStyle name="Comma 7 3 10" xfId="641" xr:uid="{AF3C24FE-0A88-443C-9F72-43B8E520F78A}"/>
+    <cellStyle name="Comma 7 3 10 2" xfId="2231" xr:uid="{B12DE6B0-EDC2-415F-B735-A178882F1BE4}"/>
+    <cellStyle name="Comma 7 3 10 3" xfId="1994" xr:uid="{8C5AB2EE-266B-4F86-9CB7-68E275DDAC0A}"/>
     <cellStyle name="Comma 7 3 11" xfId="642" xr:uid="{67025770-A3C7-4A76-BA4B-DF65EA1ABF45}"/>
+    <cellStyle name="Comma 7 3 11 2" xfId="2232" xr:uid="{78067520-DE06-4F20-A3EE-393EAC12CD24}"/>
+    <cellStyle name="Comma 7 3 11 3" xfId="1995" xr:uid="{31B5E47D-9B9D-4394-98EA-FEF0D8757A03}"/>
     <cellStyle name="Comma 7 3 12" xfId="643" xr:uid="{12D47653-899B-438E-8C5E-ED711EECBD09}"/>
+    <cellStyle name="Comma 7 3 12 2" xfId="2233" xr:uid="{2703CFDB-F590-49D8-BFDE-2F520965AC72}"/>
+    <cellStyle name="Comma 7 3 12 3" xfId="1996" xr:uid="{BB45362F-25B9-4928-A670-BFA6046374A4}"/>
     <cellStyle name="Comma 7 3 13" xfId="644" xr:uid="{92E52E42-DB84-440D-91B3-783476CB5D8E}"/>
+    <cellStyle name="Comma 7 3 13 2" xfId="2234" xr:uid="{3638F1C9-1D28-4095-8EAE-5F0064253ECD}"/>
+    <cellStyle name="Comma 7 3 13 3" xfId="1997" xr:uid="{CC9D168B-1568-4652-9929-9214A3C35DC9}"/>
     <cellStyle name="Comma 7 3 14" xfId="645" xr:uid="{425A52B9-9755-4253-B823-8F5A173712B9}"/>
+    <cellStyle name="Comma 7 3 14 2" xfId="2235" xr:uid="{E7F726D1-CB2B-4820-9E4D-0A73AEE155C1}"/>
+    <cellStyle name="Comma 7 3 14 3" xfId="1998" xr:uid="{1026C5D1-BBFC-4B81-B4AC-D3034D1CB0F7}"/>
     <cellStyle name="Comma 7 3 15" xfId="646" xr:uid="{BB8907DD-ED6C-4EB2-AD61-0222490D6D0C}"/>
+    <cellStyle name="Comma 7 3 15 2" xfId="2236" xr:uid="{9F7E75F6-3420-4568-97DA-52E2DC8D5E2C}"/>
+    <cellStyle name="Comma 7 3 15 3" xfId="1999" xr:uid="{1BB2246A-7A74-4BF6-9506-29734EFAC51F}"/>
+    <cellStyle name="Comma 7 3 16" xfId="2230" xr:uid="{7D3887A3-7F7B-459A-B774-23C948BBAD12}"/>
+    <cellStyle name="Comma 7 3 17" xfId="1993" xr:uid="{2720D131-D286-4427-BB06-B75416DF5466}"/>
     <cellStyle name="Comma 7 3 2" xfId="647" xr:uid="{85037995-B299-4E27-90B6-668007B5B20E}"/>
+    <cellStyle name="Comma 7 3 2 2" xfId="2237" xr:uid="{8336553A-5DB2-4CDF-83BE-E1C58DE6C821}"/>
+    <cellStyle name="Comma 7 3 2 3" xfId="2000" xr:uid="{E0F16176-E599-4CA8-8235-0F2DC094EDDB}"/>
     <cellStyle name="Comma 7 3 3" xfId="648" xr:uid="{ABD1E40A-C6CD-4232-8A0C-67FD92601224}"/>
+    <cellStyle name="Comma 7 3 3 2" xfId="2238" xr:uid="{6F6E4322-B0A3-457C-BAF6-299E27DA71DF}"/>
+    <cellStyle name="Comma 7 3 3 3" xfId="2001" xr:uid="{4918BD58-09A2-4FBA-8FF4-476AC1614342}"/>
     <cellStyle name="Comma 7 3 4" xfId="649" xr:uid="{53DEEBAD-B467-4FF0-AE20-D0EFEC062D25}"/>
+    <cellStyle name="Comma 7 3 4 2" xfId="2239" xr:uid="{17C1E725-AF90-442D-9F68-4C8308D409A5}"/>
+    <cellStyle name="Comma 7 3 4 3" xfId="2002" xr:uid="{99067F14-C89D-4ACD-B8FE-FEB08F59B1AF}"/>
     <cellStyle name="Comma 7 3 5" xfId="650" xr:uid="{23691EB2-F3C7-4F3C-AF31-41B45786FF5C}"/>
+    <cellStyle name="Comma 7 3 5 2" xfId="2240" xr:uid="{79D539A3-EAF2-4F4F-A8A9-DD0079D9B322}"/>
+    <cellStyle name="Comma 7 3 5 3" xfId="2003" xr:uid="{FC39A35C-5303-4D2F-96C3-5052F91C383B}"/>
     <cellStyle name="Comma 7 3 6" xfId="651" xr:uid="{2F0BC24B-0D3A-4A3A-BDB2-63C3D7E4E16B}"/>
+    <cellStyle name="Comma 7 3 6 2" xfId="2241" xr:uid="{5E2F448F-C444-4B68-A0AB-1CABF419F81E}"/>
+    <cellStyle name="Comma 7 3 6 3" xfId="2004" xr:uid="{B17C3DFE-9052-49E3-9FC4-34093A617CD1}"/>
     <cellStyle name="Comma 7 3 7" xfId="652" xr:uid="{3440FC10-FBC4-49E3-8097-847A09171A82}"/>
+    <cellStyle name="Comma 7 3 7 2" xfId="2242" xr:uid="{78E391C2-8993-494D-AF88-8AFA90F0099D}"/>
+    <cellStyle name="Comma 7 3 7 3" xfId="2005" xr:uid="{D1DD9B27-9A9E-4A83-82F1-26076D6BC77D}"/>
     <cellStyle name="Comma 7 3 8" xfId="653" xr:uid="{BB8B34A3-0EC0-4251-B9D3-E5C113CB5BF5}"/>
+    <cellStyle name="Comma 7 3 8 2" xfId="2243" xr:uid="{BE27AD45-4B04-45C3-B5A4-22D0FB4E704D}"/>
+    <cellStyle name="Comma 7 3 8 3" xfId="2006" xr:uid="{B3B295D7-1B3A-439E-96B4-9F1407DF88F1}"/>
     <cellStyle name="Comma 7 3 9" xfId="654" xr:uid="{A9F95220-1FF8-4A0F-A943-22D402FB0EB4}"/>
+    <cellStyle name="Comma 7 3 9 2" xfId="2244" xr:uid="{E6F336FB-B25D-44EE-A73B-A36331873D0D}"/>
+    <cellStyle name="Comma 7 3 9 3" xfId="2007" xr:uid="{A330BF2B-C461-42CE-8E86-5FE20863EBCA}"/>
     <cellStyle name="Comma 7 4" xfId="655" xr:uid="{E8E02416-254C-4A7D-BE2E-7732A7155EEA}"/>
+    <cellStyle name="Comma 7 4 2" xfId="2245" xr:uid="{BA198E57-98AB-4572-AC43-1D248739BBA0}"/>
+    <cellStyle name="Comma 7 4 3" xfId="2008" xr:uid="{D8995C4C-29CD-4E1C-87B9-718A00F121F3}"/>
     <cellStyle name="Comma 7 5" xfId="656" xr:uid="{528801A7-4324-4473-A78E-211B06744175}"/>
+    <cellStyle name="Comma 7 5 2" xfId="2246" xr:uid="{54B36911-B325-408A-A9F5-2AEEF227E313}"/>
+    <cellStyle name="Comma 7 5 3" xfId="2009" xr:uid="{E92D5C72-E5FA-4039-A887-3DC13426F532}"/>
     <cellStyle name="Comma 7 6" xfId="657" xr:uid="{D9BEF22F-B3AD-4771-A34F-AF92D03A7136}"/>
+    <cellStyle name="Comma 7 6 2" xfId="2247" xr:uid="{7F0D99C4-AE07-424B-A456-0656FC690A1E}"/>
+    <cellStyle name="Comma 7 6 3" xfId="2010" xr:uid="{0A8444E8-D59C-40A2-8DBD-1DCEF7C07503}"/>
     <cellStyle name="Comma 7 7" xfId="658" xr:uid="{FA3E466E-744F-4718-93B2-4C2BBF18B24B}"/>
+    <cellStyle name="Comma 7 7 2" xfId="2248" xr:uid="{AB0407D3-F481-428D-B06F-B9EB9B5A3825}"/>
+    <cellStyle name="Comma 7 7 3" xfId="2011" xr:uid="{6456C974-4226-4FA1-86E8-B0900D3295C3}"/>
     <cellStyle name="Comma 7 8" xfId="659" xr:uid="{CB36A185-E6B7-4E90-A181-87659FBD6E85}"/>
+    <cellStyle name="Comma 7 8 2" xfId="2249" xr:uid="{18CD4F1F-CBB8-4AF5-A100-7EC34BA6A409}"/>
+    <cellStyle name="Comma 7 8 3" xfId="2012" xr:uid="{F178E70D-4C4C-4B54-B409-D14C7DDB06BA}"/>
     <cellStyle name="Comma 7 9" xfId="660" xr:uid="{CF26CE83-D197-4359-AF80-C569183E0C05}"/>
+    <cellStyle name="Comma 7 9 2" xfId="2250" xr:uid="{6D9B2438-FA85-46C0-8C29-8B0E0DBBB1EF}"/>
+    <cellStyle name="Comma 7 9 3" xfId="2013" xr:uid="{122BBE2A-7168-4234-AE82-D295193937F7}"/>
     <cellStyle name="Comma 8" xfId="661" xr:uid="{8970B9F4-F7F5-4049-93B4-24A268A0D706}"/>
     <cellStyle name="Comma 8 2" xfId="662" xr:uid="{04DE7D1D-D45B-4FDA-AF30-7AE0E78D22FF}"/>
+    <cellStyle name="Comma 8 2 2" xfId="2251" xr:uid="{E337A98F-2756-4A6D-A74F-A60ADB0A5661}"/>
+    <cellStyle name="Comma 8 2 3" xfId="2014" xr:uid="{3039DD3E-E308-477F-B624-8B1DAEB6ED45}"/>
     <cellStyle name="Comma 8 3" xfId="663" xr:uid="{6863CE0C-1DB2-42C7-B2D4-5D1EF4B1B8B4}"/>
+    <cellStyle name="Comma 8 3 2" xfId="2252" xr:uid="{143E7426-FAFE-4D64-9994-8DFE5D45D337}"/>
+    <cellStyle name="Comma 8 3 3" xfId="2015" xr:uid="{36EAAC02-F679-4EF7-9F44-7953167749BC}"/>
     <cellStyle name="Comma 8 4" xfId="664" xr:uid="{1DC1653F-72CC-4954-BF90-2F58EA6E5B01}"/>
+    <cellStyle name="Comma 8 4 2" xfId="2253" xr:uid="{A2394AA3-44BC-48AD-85CB-90927D435B5C}"/>
+    <cellStyle name="Comma 8 4 3" xfId="2016" xr:uid="{D82C1B08-9F90-4333-BF9C-7D5E6942B8CF}"/>
     <cellStyle name="Comma 8 5" xfId="665" xr:uid="{0E6AEFF3-4C0F-412F-A614-07C03B783CC4}"/>
+    <cellStyle name="Comma 8 5 2" xfId="2254" xr:uid="{514196F8-E1FB-4CAD-A16B-720D2183B493}"/>
+    <cellStyle name="Comma 8 5 3" xfId="2017" xr:uid="{93C9FAA7-AE8F-49DA-ADC6-2703EC7C644A}"/>
     <cellStyle name="Comma 8 6" xfId="666" xr:uid="{D1AB91A6-9D99-489A-B5D6-92ED720ED255}"/>
+    <cellStyle name="Comma 8 6 2" xfId="2255" xr:uid="{45678D34-C309-41CC-9C08-051D6C69B660}"/>
+    <cellStyle name="Comma 8 6 3" xfId="2018" xr:uid="{CBA7B4DD-D213-4ADA-81E7-2288DC5B0174}"/>
     <cellStyle name="Comma 8 7" xfId="667" xr:uid="{3DE6C0A7-1E52-4E4F-BEEB-FDCDCF1F61DA}"/>
+    <cellStyle name="Comma 8 7 2" xfId="2256" xr:uid="{38779226-0774-4DD2-8D1C-F36904B80529}"/>
+    <cellStyle name="Comma 8 7 3" xfId="2019" xr:uid="{CE36894E-4C44-47B1-B46A-E992D2243BDE}"/>
     <cellStyle name="Comma 8 8" xfId="668" xr:uid="{71C3166F-9739-44FD-AB6A-F3ED53C019C7}"/>
+    <cellStyle name="Comma 8 8 2" xfId="2257" xr:uid="{5E9042C4-2F6E-471C-AA82-9420627B65C0}"/>
+    <cellStyle name="Comma 8 8 3" xfId="2020" xr:uid="{1B08085F-20C9-4AFD-8C2D-2BE6CA7E1381}"/>
     <cellStyle name="Comma 9" xfId="669" xr:uid="{08D28D30-81E7-4AE6-A651-08D519D74478}"/>
+    <cellStyle name="Comma 9 10" xfId="2258" xr:uid="{EA224EF1-B114-451E-BB6D-CFC3E36B37F7}"/>
+    <cellStyle name="Comma 9 11" xfId="2021" xr:uid="{E444DD34-2E84-4714-9B78-5207BE7F8860}"/>
     <cellStyle name="Comma 9 2" xfId="670" xr:uid="{182754A9-DB54-4DEC-9E4C-2979A5B06EC6}"/>
+    <cellStyle name="Comma 9 2 2" xfId="2259" xr:uid="{3CBA0348-C957-47A8-BD55-4E4E00ED5C6D}"/>
+    <cellStyle name="Comma 9 2 3" xfId="2022" xr:uid="{C9E77579-700E-4ECC-8BBF-E4FC6EA8BB67}"/>
     <cellStyle name="Comma 9 3" xfId="671" xr:uid="{23E77985-90FD-41F3-942E-BE4D865241F3}"/>
+    <cellStyle name="Comma 9 3 2" xfId="2260" xr:uid="{2B53635B-37CE-4581-994C-49F7A7564AC3}"/>
+    <cellStyle name="Comma 9 3 3" xfId="2023" xr:uid="{E90908A9-BB79-456E-A79D-F302FAC64146}"/>
     <cellStyle name="Comma 9 4" xfId="672" xr:uid="{B49F4E46-6F34-4E0B-9F2A-D7C042059602}"/>
+    <cellStyle name="Comma 9 4 2" xfId="2261" xr:uid="{BF2DA763-8117-4FF9-9293-C81F5D5C3881}"/>
+    <cellStyle name="Comma 9 4 3" xfId="2024" xr:uid="{A5EF9121-E4C3-4A76-9869-E969965C59FF}"/>
     <cellStyle name="Comma 9 5" xfId="673" xr:uid="{EC4CB72B-ED1D-421F-A743-3AE8EC9437C9}"/>
+    <cellStyle name="Comma 9 5 2" xfId="2262" xr:uid="{EB10A30E-1FC4-485A-8FC6-C46BDE0BE6FB}"/>
+    <cellStyle name="Comma 9 5 3" xfId="2025" xr:uid="{C27CDE77-3ADD-4162-93C4-41CDC9D8CF0F}"/>
     <cellStyle name="Comma 9 6" xfId="674" xr:uid="{1E83BC5B-0519-41AA-917F-E130CE8215B1}"/>
+    <cellStyle name="Comma 9 6 2" xfId="2263" xr:uid="{5CDB5846-E988-497E-A6DB-A232F5A05AE6}"/>
+    <cellStyle name="Comma 9 6 3" xfId="2026" xr:uid="{11A17CD1-A1AB-4581-B45F-2361C4FD186D}"/>
     <cellStyle name="Comma 9 7" xfId="675" xr:uid="{ADEF4189-802E-4D97-950C-995745272A68}"/>
+    <cellStyle name="Comma 9 7 2" xfId="2264" xr:uid="{39909D3A-CDBF-4843-B37F-62B03FDCC269}"/>
+    <cellStyle name="Comma 9 7 3" xfId="2027" xr:uid="{DDC1A0DD-1E7A-408B-B6F2-9BD071B3F034}"/>
     <cellStyle name="Comma 9 8" xfId="676" xr:uid="{819BF3DD-33AF-47CA-9891-02E3BB06066B}"/>
+    <cellStyle name="Comma 9 8 2" xfId="2265" xr:uid="{D834C715-FE5D-4AFB-B4F0-3EE88DDCC316}"/>
+    <cellStyle name="Comma 9 8 3" xfId="2028" xr:uid="{F9B603D4-FCD3-4AFD-8AB0-01CEDB75BF0A}"/>
     <cellStyle name="Comma 9 9" xfId="677" xr:uid="{9B07FB7B-8DCB-4437-8630-0DD701359CB0}"/>
+    <cellStyle name="Comma 9 9 2" xfId="2266" xr:uid="{9590253F-35EA-415F-A236-A711913E1C51}"/>
+    <cellStyle name="Comma 9 9 3" xfId="2029" xr:uid="{2BD0CB53-C487-47DF-A2B6-BA710216F620}"/>
     <cellStyle name="Currency 2 2" xfId="678" xr:uid="{804B9E3C-B2A4-4095-9787-FA8E3AAAEDF3}"/>
     <cellStyle name="CustomizationCells" xfId="679" xr:uid="{BBB82A5E-A4CA-4C83-868F-13BBDEE5B089}"/>
     <cellStyle name="Euro" xfId="680" xr:uid="{4D64133C-5E9A-4C89-93B3-61137BE3D1CD}"/>
@@ -5396,7 +6344,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -5457,9 +6405,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1186357</xdr:colOff>
+      <xdr:colOff>1185087</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>90129</xdr:rowOff>
+      <xdr:rowOff>87589</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5784,17 +6732,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43ACE639-45BB-4BC0-8EFB-335579A1276F}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="4" width="21.7265625" customWidth="1"/>
-    <col min="5" max="6" width="14.1796875" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" customWidth="1"/>
-    <col min="8" max="10" width="8.1796875" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" customWidth="1"/>
-    <col min="12" max="12" width="8.1796875" customWidth="1"/>
+    <col min="1" max="4" width="21.77734375" customWidth="1"/>
+    <col min="5" max="6" width="14.21875" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" customWidth="1"/>
+    <col min="8" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="9.77734375" customWidth="1"/>
+    <col min="12" max="12" width="8.21875" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.36328125" customWidth="1"/>
-    <col min="15" max="15" width="13.36328125" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -8627,36 +9575,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C030FF-C503-4743-9DBD-437AEB1E949D}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" customWidth="1"/>
-    <col min="3" max="3" width="3.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.54296875" customWidth="1"/>
-    <col min="25" max="25" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
+    <col min="3" max="3" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" customWidth="1"/>
+    <col min="25" max="25" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.21875" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30">
@@ -9369,7 +10316,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -9388,14 +10335,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011941A8-04BF-45E8-9F60-D4E07475AB4A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B4:G26"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9500,16 +10447,16 @@
         <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -9667,19 +10614,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9318C9B-7F0A-410C-BCB5-F22D93E1F454}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -9763,7 +10710,7 @@
       </c>
       <c r="C7" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,2,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D7" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,2,FALSE)</f>
@@ -9794,7 +10741,7 @@
         <v>Carbon budget 165 Mt 2021-2025 - Single</v>
       </c>
       <c r="N7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9804,7 +10751,7 @@
       </c>
       <c r="C8" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,3,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D8" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,3,FALSE)</f>
@@ -9835,7 +10782,7 @@
         <v>Carbon budget 109 Mt 2026-2030 - Single</v>
       </c>
       <c r="N8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -9848,19 +10795,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EC2971-91FC-4261-B0BB-58C7F43C1746}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -9876,7 +10823,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="B3" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -9944,7 +10891,7 @@
       </c>
       <c r="C7" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,2,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D7" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,2,FALSE)</f>
@@ -9981,7 +10928,7 @@
       </c>
       <c r="C8" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,2,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D8" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,2,FALSE)</f>
@@ -10008,7 +10955,7 @@
       </c>
       <c r="C9" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,3,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D9" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,3,FALSE)</f>
@@ -10045,7 +10992,7 @@
       </c>
       <c r="C10" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,3,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D10" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,3,FALSE)</f>
@@ -10072,7 +11019,7 @@
       </c>
       <c r="C11" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,4,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D11" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,4,FALSE)</f>
@@ -10109,7 +11056,7 @@
       </c>
       <c r="C12" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,4,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D12" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,4,FALSE)</f>
@@ -10136,7 +11083,7 @@
       </c>
       <c r="C13" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,5,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D13" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,5,FALSE)</f>
@@ -10173,7 +11120,7 @@
       </c>
       <c r="C14" t="str">
         <f>VLOOKUP(C$5, config!$B$4:$F$14,5,FALSE)</f>
-        <v>TOTCO2</v>
+        <v>TOTCO2INT</v>
       </c>
       <c r="D14" t="str">
         <f>VLOOKUP(D$5, config!$B$4:$F$14,5,FALSE)</f>
@@ -10202,17 +11149,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2314F01-B0DB-448B-9217-DEB90E2D1CCA}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:I12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
       <c r="B2" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15" thickBot="1">
@@ -10286,10 +11233,10 @@
         <v>74</v>
       </c>
       <c r="F8" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="39" t="s">
         <v>114</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>115</v>
       </c>
       <c r="H8" s="39" t="s">
         <v>81</v>
@@ -10300,7 +11247,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="C9" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>88</v>
@@ -10314,12 +11261,12 @@
       <c r="G9" s="36"/>
       <c r="H9" s="36"/>
       <c r="I9" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="2:9">
       <c r="C10" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>88</v>
@@ -10331,15 +11278,15 @@
       <c r="G10" s="36"/>
       <c r="H10" s="36"/>
       <c r="I10" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="C11" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="36">
         <v>0</v>
@@ -10350,15 +11297,15 @@
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
       <c r="I11" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="2:9">
       <c r="C12" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="40">
@@ -10367,7 +11314,7 @@
       <c r="G12" s="36"/>
       <c r="H12" s="36"/>
       <c r="I12" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
